--- a/data/latest_data.xlsx
+++ b/data/latest_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\고객센터 평가\2026년 03월\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\고객센터 평가\2026년 04월\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4195280-A12E-4004-9DA7-D3780A03D88D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD30030C-A46F-4E61-A5DC-FD8B9E0A74DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{374363BE-A5F5-4ADC-8A41-9D43B010FE25}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="37">
   <si>
     <t>센터명</t>
   </si>
@@ -144,6 +144,10 @@
   </si>
   <si>
     <t>총점</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>퇴계원/별내</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -594,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576B49EF-D72C-489F-81B1-8DBFDE47B864}">
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="20.625" customWidth="1"/>
@@ -3374,6 +3378,880 @@
         <v>689.85491217368076</v>
       </c>
     </row>
+    <row r="74" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C74" s="3">
+        <v>0.5484281675373065</v>
+      </c>
+      <c r="D74" s="3">
+        <v>0.50536864710093055</v>
+      </c>
+      <c r="E74" s="3">
+        <v>0.8694369884349008</v>
+      </c>
+      <c r="F74" s="3">
+        <v>1</v>
+      </c>
+      <c r="G74" s="3">
+        <v>1</v>
+      </c>
+      <c r="H74" s="2">
+        <v>94.958428571428584</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="2">
+        <v>0</v>
+      </c>
+      <c r="K74" s="2">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>692.13078542704022</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B75" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C75" s="3">
+        <v>0.51957307508695361</v>
+      </c>
+      <c r="D75" s="3">
+        <v>0.70114006514657978</v>
+      </c>
+      <c r="E75" s="3">
+        <v>0.84944309084580583</v>
+      </c>
+      <c r="F75" s="3">
+        <v>0.96463513284456737</v>
+      </c>
+      <c r="G75" s="3">
+        <v>1</v>
+      </c>
+      <c r="H75" s="2">
+        <v>93.595013169446915</v>
+      </c>
+      <c r="I75" s="2">
+        <v>0</v>
+      </c>
+      <c r="J75" s="2">
+        <v>0</v>
+      </c>
+      <c r="K75" s="2">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>690.93772426638611</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B76" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C76" s="3">
+        <v>0.43382855444956175</v>
+      </c>
+      <c r="D76" s="3">
+        <v>0.82736720554272514</v>
+      </c>
+      <c r="E76" s="3">
+        <v>0.82983169994141959</v>
+      </c>
+      <c r="F76" s="3">
+        <v>1</v>
+      </c>
+      <c r="G76" s="3">
+        <v>1</v>
+      </c>
+      <c r="H76" s="2">
+        <v>93.185838509316781</v>
+      </c>
+      <c r="I76" s="2">
+        <v>0</v>
+      </c>
+      <c r="J76" s="2">
+        <v>0</v>
+      </c>
+      <c r="K76" s="2">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>659.52826401084826</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B77" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C77" s="3">
+        <v>0.63180318856514572</v>
+      </c>
+      <c r="D77" s="3">
+        <v>0.9582210242587601</v>
+      </c>
+      <c r="E77" s="3">
+        <v>0.92219730557885549</v>
+      </c>
+      <c r="F77" s="3">
+        <v>0.93363800072295822</v>
+      </c>
+      <c r="G77" s="3">
+        <v>1</v>
+      </c>
+      <c r="H77" s="2">
+        <v>92.136634278002717</v>
+      </c>
+      <c r="I77" s="2">
+        <v>0</v>
+      </c>
+      <c r="J77" s="2">
+        <v>0</v>
+      </c>
+      <c r="K77" s="2">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>778.81429048700466</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C78" s="3">
+        <v>0.58596046093667409</v>
+      </c>
+      <c r="D78" s="3">
+        <v>0.86286201022146503</v>
+      </c>
+      <c r="E78" s="3">
+        <v>0.87454990944923827</v>
+      </c>
+      <c r="F78" s="3">
+        <v>0.96260881855393221</v>
+      </c>
+      <c r="G78" s="3">
+        <v>1</v>
+      </c>
+      <c r="H78" s="2">
+        <v>94.595636363636373</v>
+      </c>
+      <c r="I78" s="2">
+        <v>0</v>
+      </c>
+      <c r="J78" s="2">
+        <v>0</v>
+      </c>
+      <c r="K78" s="2">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>744.42097275634683</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B79" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C79" s="3">
+        <v>0.55256084271703598</v>
+      </c>
+      <c r="D79" s="3">
+        <v>0.97872340425531912</v>
+      </c>
+      <c r="E79" s="3">
+        <v>0.87578471903230748</v>
+      </c>
+      <c r="F79" s="3">
+        <v>0.94902703628156626</v>
+      </c>
+      <c r="G79" s="3">
+        <v>1</v>
+      </c>
+      <c r="H79" s="2">
+        <v>93.854276612276635</v>
+      </c>
+      <c r="I79" s="2">
+        <v>0</v>
+      </c>
+      <c r="J79" s="2">
+        <v>0</v>
+      </c>
+      <c r="K79" s="2">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>735.53778416033492</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B80" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C80" s="3">
+        <v>0.48391309509675889</v>
+      </c>
+      <c r="D80" s="3">
+        <v>0.97623862487360968</v>
+      </c>
+      <c r="E80" s="3">
+        <v>0.86501877458046372</v>
+      </c>
+      <c r="F80" s="3">
+        <v>0.99990395455184011</v>
+      </c>
+      <c r="G80" s="3">
+        <v>1</v>
+      </c>
+      <c r="H80" s="2">
+        <v>92.995511508951424</v>
+      </c>
+      <c r="I80" s="2">
+        <v>0</v>
+      </c>
+      <c r="J80" s="2">
+        <v>0</v>
+      </c>
+      <c r="K80" s="2">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>701.76197175471373</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B81" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C81" s="3">
+        <v>0.49605578484888829</v>
+      </c>
+      <c r="D81" s="3">
+        <v>0.78562653562653562</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0.90728911294499504</v>
+      </c>
+      <c r="F81" s="3">
+        <v>0.95529138902540855</v>
+      </c>
+      <c r="G81" s="3">
+        <v>1</v>
+      </c>
+      <c r="H81" s="2">
+        <v>93.237562804649414</v>
+      </c>
+      <c r="I81" s="2">
+        <v>0</v>
+      </c>
+      <c r="J81" s="2">
+        <v>0</v>
+      </c>
+      <c r="K81" s="2">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>690.16003693673235</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B82" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C82" s="3">
+        <v>0.45128733264675591</v>
+      </c>
+      <c r="D82" s="3">
+        <v>0.59603246167718671</v>
+      </c>
+      <c r="E82" s="3">
+        <v>0.85795016696634985</v>
+      </c>
+      <c r="F82" s="3">
+        <v>0.83462242673732301</v>
+      </c>
+      <c r="G82" s="3">
+        <v>0.98568925709225197</v>
+      </c>
+      <c r="H82" s="2">
+        <v>93.053026026604968</v>
+      </c>
+      <c r="I82" s="2">
+        <v>0</v>
+      </c>
+      <c r="J82" s="2">
+        <v>0</v>
+      </c>
+      <c r="K82" s="2">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>627.89547353299679</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B83" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C83" s="3">
+        <v>0.56972850303047073</v>
+      </c>
+      <c r="D83" s="3">
+        <v>0.89600223651104283</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0.89266339821879259</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0.99776810975900843</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1</v>
+      </c>
+      <c r="H83" s="2">
+        <v>94.498769230769241</v>
+      </c>
+      <c r="I83" s="2">
+        <v>0</v>
+      </c>
+      <c r="J83" s="2">
+        <v>0</v>
+      </c>
+      <c r="K83" s="2">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>742.22648052453326</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B84" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C84" s="3">
+        <v>0.58401353772645825</v>
+      </c>
+      <c r="D84" s="3">
+        <v>0.58935574229691878</v>
+      </c>
+      <c r="E84" s="3">
+        <v>0.86126215757243085</v>
+      </c>
+      <c r="F84" s="3">
+        <v>0.94167096775404946</v>
+      </c>
+      <c r="G84" s="3">
+        <v>1</v>
+      </c>
+      <c r="H84" s="2">
+        <v>94.772004329004332</v>
+      </c>
+      <c r="I84" s="2">
+        <v>0</v>
+      </c>
+      <c r="J84" s="2">
+        <v>0</v>
+      </c>
+      <c r="K84" s="2">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>714.08212108365319</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C85" s="3">
+        <v>0.4812655540279494</v>
+      </c>
+      <c r="D85" s="3">
+        <v>0.98968407479045772</v>
+      </c>
+      <c r="E85" s="3">
+        <v>0.88582834331337323</v>
+      </c>
+      <c r="F85" s="3">
+        <v>0.98490484758105135</v>
+      </c>
+      <c r="G85" s="3">
+        <v>1</v>
+      </c>
+      <c r="H85" s="2">
+        <v>91.439023959646917</v>
+      </c>
+      <c r="I85" s="2">
+        <v>0</v>
+      </c>
+      <c r="J85" s="2">
+        <v>0</v>
+      </c>
+      <c r="K85" s="2">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>698.59397091216988</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B86" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C86" s="3">
+        <v>0.47897282301819166</v>
+      </c>
+      <c r="D86" s="3">
+        <v>0.77348484848484844</v>
+      </c>
+      <c r="E86" s="3">
+        <v>0.81479138996057598</v>
+      </c>
+      <c r="F86" s="3">
+        <v>0.92733999684665946</v>
+      </c>
+      <c r="G86" s="3">
+        <v>1</v>
+      </c>
+      <c r="H86" s="2">
+        <v>94.267616683217483</v>
+      </c>
+      <c r="I86" s="2">
+        <v>0</v>
+      </c>
+      <c r="J86" s="2">
+        <v>0</v>
+      </c>
+      <c r="K86" s="2">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>672.78515387637367</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B87" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C87" s="3">
+        <v>0.52504311831666095</v>
+      </c>
+      <c r="D87" s="3">
+        <v>0.99045194143857418</v>
+      </c>
+      <c r="E87" s="3">
+        <v>0.8367383416447709</v>
+      </c>
+      <c r="F87" s="3">
+        <v>0.98462444949542838</v>
+      </c>
+      <c r="G87" s="3">
+        <v>1</v>
+      </c>
+      <c r="H87" s="2">
+        <v>95.039720034995639</v>
+      </c>
+      <c r="I87" s="2">
+        <v>0</v>
+      </c>
+      <c r="J87" s="2">
+        <v>0</v>
+      </c>
+      <c r="K87" s="2">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>726.32107420255943</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C88" s="3">
+        <v>0.56368256385637905</v>
+      </c>
+      <c r="D88" s="3">
+        <v>0.6753750646663218</v>
+      </c>
+      <c r="E88" s="3">
+        <v>0.86875769279741943</v>
+      </c>
+      <c r="F88" s="3">
+        <v>1</v>
+      </c>
+      <c r="G88" s="3">
+        <v>1</v>
+      </c>
+      <c r="H88" s="2">
+        <v>93.030804093567269</v>
+      </c>
+      <c r="I88" s="2">
+        <v>0</v>
+      </c>
+      <c r="J88" s="2">
+        <v>0</v>
+      </c>
+      <c r="K88" s="2">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>715.59372068120797</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B89" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C89" s="3">
+        <v>0.49185047391265835</v>
+      </c>
+      <c r="D89" s="3">
+        <v>0.53326713008937443</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0.84454361654913945</v>
+      </c>
+      <c r="F89" s="3">
+        <v>1</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1</v>
+      </c>
+      <c r="H89" s="2">
+        <v>92.753793706293692</v>
+      </c>
+      <c r="I89" s="2">
+        <v>0</v>
+      </c>
+      <c r="J89" s="2">
+        <v>0</v>
+      </c>
+      <c r="K89" s="2">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>661.59826736719322</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B90" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C90" s="3">
+        <v>0.52746248557137365</v>
+      </c>
+      <c r="D90" s="3">
+        <v>0.54736842105263162</v>
+      </c>
+      <c r="E90" s="3">
+        <v>0.90163357480130213</v>
+      </c>
+      <c r="F90" s="3">
+        <v>0.89201568185483604</v>
+      </c>
+      <c r="G90" s="3">
+        <v>1</v>
+      </c>
+      <c r="H90" s="2">
+        <v>93.219837728194719</v>
+      </c>
+      <c r="I90" s="2">
+        <v>0</v>
+      </c>
+      <c r="J90" s="2">
+        <v>0</v>
+      </c>
+      <c r="K90" s="2">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>677.26261508319703</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B91" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C91" s="3">
+        <v>0.51862608722236658</v>
+      </c>
+      <c r="D91" s="3">
+        <v>0.99044724272687801</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0.91764743558950213</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0.98205048269381079</v>
+      </c>
+      <c r="G91" s="3">
+        <v>1</v>
+      </c>
+      <c r="H91" s="2">
+        <v>95.772251655629148</v>
+      </c>
+      <c r="I91" s="2">
+        <v>0</v>
+      </c>
+      <c r="J91" s="2">
+        <v>0</v>
+      </c>
+      <c r="K91" s="2">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>728.26637216999961</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B92" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C92" s="3">
+        <v>0.54859657157812092</v>
+      </c>
+      <c r="D92" s="3">
+        <v>0.69421487603305787</v>
+      </c>
+      <c r="E92" s="3">
+        <v>0.89613654632210837</v>
+      </c>
+      <c r="F92" s="3">
+        <v>1</v>
+      </c>
+      <c r="G92" s="3">
+        <v>1</v>
+      </c>
+      <c r="H92" s="2">
+        <v>93.999322725418196</v>
+      </c>
+      <c r="I92" s="2">
+        <v>0</v>
+      </c>
+      <c r="J92" s="2">
+        <v>0</v>
+      </c>
+      <c r="K92" s="2">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>710.14892469669053</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B93" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C93" s="3">
+        <v>0.58242145443868065</v>
+      </c>
+      <c r="D93" s="3">
+        <v>0.70774647887323938</v>
+      </c>
+      <c r="E93" s="3">
+        <v>0.82415742097550759</v>
+      </c>
+      <c r="F93" s="3">
+        <v>1</v>
+      </c>
+      <c r="G93" s="3">
+        <v>1</v>
+      </c>
+      <c r="H93" s="2">
+        <v>93.905495652173911</v>
+      </c>
+      <c r="I93" s="2">
+        <v>0</v>
+      </c>
+      <c r="J93" s="2">
+        <v>0</v>
+      </c>
+      <c r="K93" s="2">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>730.01194348077229</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B94" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C94" s="3">
+        <v>0.67237607174534342</v>
+      </c>
+      <c r="D94" s="3">
+        <v>0.96051889452904682</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0.90544147843942502</v>
+      </c>
+      <c r="F94" s="3">
+        <v>1</v>
+      </c>
+      <c r="G94" s="3">
+        <v>1</v>
+      </c>
+      <c r="H94" s="2">
+        <v>93.720251415941433</v>
+      </c>
+      <c r="I94" s="2">
+        <v>0</v>
+      </c>
+      <c r="J94" s="2">
+        <v>0</v>
+      </c>
+      <c r="K94" s="2">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>809.57898032878506</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B95" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C95" s="3">
+        <v>0.51675681408420826</v>
+      </c>
+      <c r="D95" s="3">
+        <v>0.71411411411411407</v>
+      </c>
+      <c r="E95" s="3">
+        <v>0.73579768775044574</v>
+      </c>
+      <c r="F95" s="3">
+        <v>1</v>
+      </c>
+      <c r="G95" s="3">
+        <v>1</v>
+      </c>
+      <c r="H95" s="2">
+        <v>93.965438596491225</v>
+      </c>
+      <c r="I95" s="2">
+        <v>0</v>
+      </c>
+      <c r="J95" s="2">
+        <v>0</v>
+      </c>
+      <c r="K95" s="2">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>689.59309775421718</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B96" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C96" s="3">
+        <v>0.61450467216868532</v>
+      </c>
+      <c r="D96" s="3">
+        <v>0.56618133686300465</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0.92023438066903707</v>
+      </c>
+      <c r="F96" s="3">
+        <v>1</v>
+      </c>
+      <c r="G96" s="3">
+        <v>1</v>
+      </c>
+      <c r="H96" s="2">
+        <v>93.454481547344642</v>
+      </c>
+      <c r="I96" s="2">
+        <v>0</v>
+      </c>
+      <c r="J96" s="2">
+        <v>0</v>
+      </c>
+      <c r="K96" s="2">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>738.05018492642193</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/latest_data.xlsx
+++ b/data/latest_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\고객센터 평가\2026년 04월\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD30030C-A46F-4E61-A5DC-FD8B9E0A74DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413CEB44-27AC-4225-8B46-510C76E2D902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{374363BE-A5F5-4ADC-8A41-9D43B010FE25}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{374363BE-A5F5-4ADC-8A41-9D43B010FE25}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3386,13 +3386,13 @@
         <v>46113</v>
       </c>
       <c r="C74" s="3">
-        <v>0.5484281675373065</v>
+        <v>0.74899361530828135</v>
       </c>
       <c r="D74" s="3">
-        <v>0.50536864710093055</v>
+        <v>0.79075577763897564</v>
       </c>
       <c r="E74" s="3">
-        <v>0.8694369884349008</v>
+        <v>0.87711709920121972</v>
       </c>
       <c r="F74" s="3">
         <v>1</v>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>692.13078542704022</v>
+        <v>830.98049475488097</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3424,13 +3424,13 @@
         <v>46113</v>
       </c>
       <c r="C75" s="3">
-        <v>0.51957307508695361</v>
+        <v>0.70327178490443798</v>
       </c>
       <c r="D75" s="3">
-        <v>0.70114006514657978</v>
+        <v>0.82152777777777775</v>
       </c>
       <c r="E75" s="3">
-        <v>0.84944309084580583</v>
+        <v>0.85210729300580246</v>
       </c>
       <c r="F75" s="3">
         <v>0.96463513284456737</v>
@@ -3451,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="L75">
-        <v>690.93772426638611</v>
+        <v>804.01078592912233</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3462,13 +3462,13 @@
         <v>46113</v>
       </c>
       <c r="C76" s="3">
-        <v>0.43382855444956175</v>
+        <v>0.58383598276630511</v>
       </c>
       <c r="D76" s="3">
-        <v>0.82736720554272514</v>
+        <v>0.87091913611250626</v>
       </c>
       <c r="E76" s="3">
-        <v>0.82983169994141959</v>
+        <v>0.82913094371856122</v>
       </c>
       <c r="F76" s="3">
         <v>1</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>659.52826401084826</v>
+        <v>746.38754264203521</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3500,13 +3500,13 @@
         <v>46113</v>
       </c>
       <c r="C77" s="3">
-        <v>0.63180318856514572</v>
+        <v>0.83124558234508761</v>
       </c>
       <c r="D77" s="3">
-        <v>0.9582210242587601</v>
+        <v>0.97681041497152155</v>
       </c>
       <c r="E77" s="3">
-        <v>0.92219730557885549</v>
+        <v>0.92144533726249422</v>
       </c>
       <c r="F77" s="3">
         <v>0.93363800072295822</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="L77">
-        <v>778.81429048700466</v>
+        <v>890.36654613724886</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3538,13 +3538,13 @@
         <v>46113</v>
       </c>
       <c r="C78" s="3">
-        <v>0.58596046093667409</v>
+        <v>0.74995242626070413</v>
       </c>
       <c r="D78" s="3">
-        <v>0.86286201022146503</v>
+        <v>0.87175893482831113</v>
       </c>
       <c r="E78" s="3">
-        <v>0.87454990944923827</v>
+        <v>0.8752319010555496</v>
       </c>
       <c r="F78" s="3">
         <v>0.96260881855393221</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="L78">
-        <v>744.42097275634683</v>
+        <v>835.50624614524793</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3576,13 +3576,13 @@
         <v>46113</v>
       </c>
       <c r="C79" s="3">
-        <v>0.55256084271703598</v>
+        <v>0.76184162731565563</v>
       </c>
       <c r="D79" s="3">
-        <v>0.97872340425531912</v>
+        <v>0.98409542743538769</v>
       </c>
       <c r="E79" s="3">
-        <v>0.87578471903230748</v>
+        <v>0.8796803740466792</v>
       </c>
       <c r="F79" s="3">
         <v>0.94902703628156626</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="L79">
-        <v>735.53778416033492</v>
+        <v>851.17941800758263</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3614,13 +3614,13 @@
         <v>46113</v>
       </c>
       <c r="C80" s="3">
-        <v>0.48391309509675889</v>
+        <v>0.66238700157731378</v>
       </c>
       <c r="D80" s="3">
-        <v>0.97623862487360968</v>
+        <v>0.98897220996912216</v>
       </c>
       <c r="E80" s="3">
-        <v>0.86501877458046372</v>
+        <v>0.8690327640914115</v>
       </c>
       <c r="F80" s="3">
         <v>0.99990395455184011</v>
@@ -3641,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>701.76197175471373</v>
+        <v>801.19597882857022</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3652,13 +3652,13 @@
         <v>46113</v>
       </c>
       <c r="C81" s="3">
-        <v>0.49605578484888829</v>
+        <v>0.66493165264243193</v>
       </c>
       <c r="D81" s="3">
-        <v>0.78562653562653562</v>
+        <v>0.80336200156372162</v>
       </c>
       <c r="E81" s="3">
-        <v>0.90728911294499504</v>
+        <v>0.91002019048827154</v>
       </c>
       <c r="F81" s="3">
         <v>0.95529138902540855</v>
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="L81">
-        <v>690.16003693673235</v>
+        <v>784.81531081690002</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3690,13 +3690,13 @@
         <v>46113</v>
       </c>
       <c r="C82" s="3">
-        <v>0.45128733264675591</v>
+        <v>0.62486096807415037</v>
       </c>
       <c r="D82" s="3">
-        <v>0.59603246167718671</v>
+        <v>0.72119258662369057</v>
       </c>
       <c r="E82" s="3">
-        <v>0.85795016696634985</v>
+        <v>0.8629348575933774</v>
       </c>
       <c r="F82" s="3">
         <v>0.83462242673732301</v>
@@ -3717,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="L82">
-        <v>627.89547353299679</v>
+        <v>735.87698551271421</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3728,13 +3728,13 @@
         <v>46113</v>
       </c>
       <c r="C83" s="3">
-        <v>0.56972850303047073</v>
+        <v>0.76187313184988381</v>
       </c>
       <c r="D83" s="3">
-        <v>0.89600223651104283</v>
+        <v>0.94627562937970411</v>
       </c>
       <c r="E83" s="3">
-        <v>0.89266339821879259</v>
+        <v>0.89607145450584558</v>
       </c>
       <c r="F83" s="3">
         <v>0.99776810975900843</v>
@@ -3755,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="L83">
-        <v>742.22648052453326</v>
+        <v>852.93336566207654</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3766,13 +3766,13 @@
         <v>46113</v>
       </c>
       <c r="C84" s="3">
-        <v>0.58401353772645825</v>
+        <v>0.7823014134979096</v>
       </c>
       <c r="D84" s="3">
-        <v>0.58935574229691878</v>
+        <v>0.68737957610789979</v>
       </c>
       <c r="E84" s="3">
-        <v>0.86126215757243085</v>
+        <v>0.86365196499056118</v>
       </c>
       <c r="F84" s="3">
         <v>0.94167096775404946</v>
@@ -3793,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="L84">
-        <v>714.08212108365319</v>
+        <v>832.94283613904952</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3804,13 +3804,13 @@
         <v>46113</v>
       </c>
       <c r="C85" s="3">
-        <v>0.4812655540279494</v>
+        <v>0.66163136736221084</v>
       </c>
       <c r="D85" s="3">
-        <v>0.98968407479045772</v>
+        <v>0.99775533108866443</v>
       </c>
       <c r="E85" s="3">
-        <v>0.88582834331337323</v>
+        <v>0.8839796047975903</v>
       </c>
       <c r="F85" s="3">
         <v>0.98490484758105135</v>
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="L85">
-        <v>698.59397091216988</v>
+        <v>798.60229387583445</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3842,13 +3842,13 @@
         <v>46113</v>
       </c>
       <c r="C86" s="3">
-        <v>0.47897282301819166</v>
+        <v>0.65460437483121792</v>
       </c>
       <c r="D86" s="3">
-        <v>0.77348484848484844</v>
+        <v>0.84887678692988433</v>
       </c>
       <c r="E86" s="3">
-        <v>0.81479138996057598</v>
+        <v>0.81628735947353992</v>
       </c>
       <c r="F86" s="3">
         <v>0.92733999684665946</v>
@@ -3869,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="L86">
-        <v>672.78515387637367</v>
+        <v>776.92170121804179</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3880,13 +3880,13 @@
         <v>46113</v>
       </c>
       <c r="C87" s="3">
-        <v>0.52504311831666095</v>
+        <v>0.71602766423483555</v>
       </c>
       <c r="D87" s="3">
-        <v>0.99045194143857418</v>
+        <v>0.99557766721945828</v>
       </c>
       <c r="E87" s="3">
-        <v>0.8367383416447709</v>
+        <v>0.83887084686485136</v>
       </c>
       <c r="F87" s="3">
         <v>0.98462444949542838</v>
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="L87">
-        <v>726.32107420255943</v>
+        <v>831.87514703564386</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3918,13 +3918,13 @@
         <v>46113</v>
       </c>
       <c r="C88" s="3">
-        <v>0.56368256385637905</v>
+        <v>0.71523494735407367</v>
       </c>
       <c r="D88" s="3">
-        <v>0.6753750646663218</v>
+        <v>0.81066330814441645</v>
       </c>
       <c r="E88" s="3">
-        <v>0.86875769279741943</v>
+        <v>0.87687611063015447</v>
       </c>
       <c r="F88" s="3">
         <v>1</v>
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="L88">
-        <v>715.59372068120797</v>
+        <v>812.47635595274937</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3956,13 +3956,13 @@
         <v>46113</v>
       </c>
       <c r="C89" s="3">
-        <v>0.49185047391265835</v>
+        <v>0.65933652227832407</v>
       </c>
       <c r="D89" s="3">
-        <v>0.53326713008937443</v>
+        <v>0.55412371134020622</v>
       </c>
       <c r="E89" s="3">
-        <v>0.84454361654913945</v>
+        <v>0.8469572658176876</v>
       </c>
       <c r="F89" s="3">
         <v>1</v>
@@ -3983,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="L89">
-        <v>661.59826736719322</v>
+        <v>755.80125209339258</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -3994,13 +3994,13 @@
         <v>46113</v>
       </c>
       <c r="C90" s="3">
-        <v>0.52746248557137365</v>
+        <v>0.71571984850909476</v>
       </c>
       <c r="D90" s="3">
-        <v>0.54736842105263162</v>
+        <v>0.66804046459348065</v>
       </c>
       <c r="E90" s="3">
-        <v>0.90163357480130213</v>
+        <v>0.89647836869661068</v>
       </c>
       <c r="F90" s="3">
         <v>0.89201568185483604</v>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="L90">
-        <v>677.26261508319703</v>
+        <v>787.8713690530285</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -4032,13 +4032,13 @@
         <v>46113</v>
       </c>
       <c r="C91" s="3">
-        <v>0.51862608722236658</v>
+        <v>0.72931411363671106</v>
       </c>
       <c r="D91" s="3">
-        <v>0.99044724272687801</v>
+        <v>0.99616858237547889</v>
       </c>
       <c r="E91" s="3">
-        <v>0.91764743558950213</v>
+        <v>0.91901639869836338</v>
       </c>
       <c r="F91" s="3">
         <v>0.98205048269381079</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="L91">
-        <v>728.26637216999961</v>
+        <v>844.7169206627492</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -4070,13 +4070,13 @@
         <v>46113</v>
       </c>
       <c r="C92" s="3">
-        <v>0.54859657157812092</v>
+        <v>0.71725333682282122</v>
       </c>
       <c r="D92" s="3">
-        <v>0.69421487603305787</v>
+        <v>0.78663396689147758</v>
       </c>
       <c r="E92" s="3">
-        <v>0.89613654632210837</v>
+        <v>0.8983248461155976</v>
       </c>
       <c r="F92" s="3">
         <v>1</v>
@@ -4097,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="L92">
-        <v>710.14892469669053</v>
+        <v>812.15205466711757</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -4108,13 +4108,13 @@
         <v>46113</v>
       </c>
       <c r="C93" s="3">
-        <v>0.58242145443868065</v>
+        <v>0.77836938435940095</v>
       </c>
       <c r="D93" s="3">
-        <v>0.70774647887323938</v>
+        <v>0.82913337430854328</v>
       </c>
       <c r="E93" s="3">
-        <v>0.82415742097550759</v>
+        <v>0.82437729431528295</v>
       </c>
       <c r="F93" s="3">
         <v>1</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="L93">
-        <v>730.01194348077229</v>
+        <v>849.9219944806988</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -4146,13 +4146,13 @@
         <v>46113</v>
       </c>
       <c r="C94" s="3">
-        <v>0.67237607174534342</v>
+        <v>0.84570809106139744</v>
       </c>
       <c r="D94" s="3">
-        <v>0.96051889452904682</v>
+        <v>0.98809523809523814</v>
       </c>
       <c r="E94" s="3">
-        <v>0.90544147843942502</v>
+        <v>0.90848038375878015</v>
       </c>
       <c r="F94" s="3">
         <v>1</v>
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="L94">
-        <v>809.57898032878506</v>
+        <v>907.66922530923387</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -4184,13 +4184,13 @@
         <v>46113</v>
       </c>
       <c r="C95" s="3">
-        <v>0.51675681408420826</v>
+        <v>0.67985859478568267</v>
       </c>
       <c r="D95" s="3">
-        <v>0.71411411411411407</v>
+        <v>0.83683105981112282</v>
       </c>
       <c r="E95" s="3">
-        <v>0.73579768775044574</v>
+        <v>0.74229125765099901</v>
       </c>
       <c r="F95" s="3">
         <v>1</v>
@@ -4211,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="L95">
-        <v>689.59309775421718</v>
+        <v>791.570771709729</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -4222,13 +4222,13 @@
         <v>46113</v>
       </c>
       <c r="C96" s="3">
-        <v>0.61450467216868532</v>
+        <v>0.83085162494421227</v>
       </c>
       <c r="D96" s="3">
-        <v>0.56618133686300465</v>
+        <v>0.77103658536585362</v>
       </c>
       <c r="E96" s="3">
-        <v>0.92023438066903707</v>
+        <v>0.91971355085985174</v>
       </c>
       <c r="F96" s="3">
         <v>1</v>
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="L96">
-        <v>738.05018492642193</v>
+        <v>877.52653380324682</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest_data.xlsx
+++ b/data/latest_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\고객센터 평가\2026년 05월\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\고객센터 평가\2026년 06월\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6635B0A2-154F-486E-B93D-A2BDF444035D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C74B681-C1F3-4FE7-A264-BF024D1FAA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{374363BE-A5F5-4ADC-8A41-9D43B010FE25}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="41">
   <si>
     <t>센터명</t>
   </si>
@@ -167,7 +167,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -653,13 +653,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576B49EF-D72C-489F-81B1-8DBFDE47B864}">
-  <dimension ref="A1:L413"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:L436"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="62.25" customHeight="1" thickBot="1">
+    <row r="1" spans="1:12" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +697,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="2" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>11</v>
       </c>
@@ -733,7 +733,7 @@
         <v>447.95</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="3" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>12</v>
       </c>
@@ -769,7 +769,7 @@
         <v>444.4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="4" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>13</v>
       </c>
@@ -805,7 +805,7 @@
         <v>412.19</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="5" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>14</v>
       </c>
@@ -841,7 +841,7 @@
         <v>505.92</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="6" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>15</v>
       </c>
@@ -877,7 +877,7 @@
         <v>469.07</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="7" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>16</v>
       </c>
@@ -913,7 +913,7 @@
         <v>462.9</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="8" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
@@ -949,7 +949,7 @@
         <v>482.45</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="9" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>18</v>
       </c>
@@ -985,7 +985,7 @@
         <v>469.48</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="10" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>19</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>452.91</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="11" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>20</v>
       </c>
@@ -1057,7 +1057,7 @@
         <v>470.93</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="12" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>21</v>
       </c>
@@ -1093,7 +1093,7 @@
         <v>457.46</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="13" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>22</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>480.39</v>
       </c>
     </row>
-    <row r="14" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="14" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>23</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>478.09</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="15" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>24</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>482.12</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="16" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>37</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>508.53</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="17" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>26</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>480.66</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="18" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>27</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>443.39</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="19" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>28</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>492.5</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="20" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>29</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>441.26</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="21" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>30</v>
       </c>
@@ -1417,7 +1417,7 @@
         <v>464.06</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="22" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>31</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>486.83</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="23" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>32</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>430.67</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="24" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>38</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>387.78</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="25" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>39</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>438.64</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="26" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>34</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>471.85</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="27" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>40</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>448.63</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="28" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
         <v>11</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>576.36</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="29" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
         <v>12</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>540.49</v>
       </c>
     </row>
-    <row r="30" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="30" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
         <v>13</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>551.99</v>
       </c>
     </row>
-    <row r="31" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="31" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
         <v>14</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>624.82000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="32" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
         <v>15</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>590.49</v>
       </c>
     </row>
-    <row r="33" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="33" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>16</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>591.23</v>
       </c>
     </row>
-    <row r="34" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="34" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
         <v>17</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>583.07000000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="35" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>18</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>589.19000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="36" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
         <v>19</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>550.09</v>
       </c>
     </row>
-    <row r="37" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="37" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
         <v>20</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>592.29999999999995</v>
       </c>
     </row>
-    <row r="38" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="38" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>21</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>590.25</v>
       </c>
     </row>
-    <row r="39" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="39" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>22</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>583.16999999999996</v>
       </c>
     </row>
-    <row r="40" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="40" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>23</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>610.48</v>
       </c>
     </row>
-    <row r="41" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="41" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
         <v>24</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>586.91</v>
       </c>
     </row>
-    <row r="42" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="42" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
         <v>37</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>649.12</v>
       </c>
     </row>
-    <row r="43" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="43" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
         <v>26</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>588.14</v>
       </c>
     </row>
-    <row r="44" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="44" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>27</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>583.84</v>
       </c>
     </row>
-    <row r="45" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="45" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>28</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>602.25</v>
       </c>
     </row>
-    <row r="46" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="46" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
         <v>29</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>559.08000000000004</v>
       </c>
     </row>
-    <row r="47" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="47" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
         <v>30</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>595.77</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="48" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
         <v>31</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>602.34</v>
       </c>
     </row>
-    <row r="49" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="49" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
         <v>32</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>547.1</v>
       </c>
     </row>
-    <row r="50" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="50" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
         <v>38</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>503.26</v>
       </c>
     </row>
-    <row r="51" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="51" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
         <v>39</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>548.6</v>
       </c>
     </row>
-    <row r="52" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="52" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
         <v>34</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>540.01</v>
       </c>
     </row>
-    <row r="53" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="53" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
         <v>40</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>587.36</v>
       </c>
     </row>
-    <row r="54" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="54" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
         <v>11</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>720.03</v>
       </c>
     </row>
-    <row r="55" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="55" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
         <v>12</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>645.54999999999995</v>
       </c>
     </row>
-    <row r="56" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="56" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
         <v>13</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>653.84</v>
       </c>
     </row>
-    <row r="57" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="57" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
         <v>14</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>746.24</v>
       </c>
     </row>
-    <row r="58" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="58" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
         <v>15</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>713.51</v>
       </c>
     </row>
-    <row r="59" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="59" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
         <v>16</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>728.67</v>
       </c>
     </row>
-    <row r="60" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="60" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
         <v>17</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>670.76</v>
       </c>
     </row>
-    <row r="61" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="61" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
         <v>18</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>695.55</v>
       </c>
     </row>
-    <row r="62" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="62" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
         <v>19</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>664.69</v>
       </c>
     </row>
-    <row r="63" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="63" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
         <v>20</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>708.07</v>
       </c>
     </row>
-    <row r="64" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="64" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
         <v>21</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>719.76</v>
       </c>
     </row>
-    <row r="65" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="65" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9" t="s">
         <v>22</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>697.09</v>
       </c>
     </row>
-    <row r="66" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="66" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
         <v>23</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>706.33</v>
       </c>
     </row>
-    <row r="67" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="67" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
         <v>24</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>693.85</v>
       </c>
     </row>
-    <row r="68" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="68" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
         <v>37</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>741.48</v>
       </c>
     </row>
-    <row r="69" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="69" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
         <v>26</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>681.7</v>
       </c>
     </row>
-    <row r="70" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="70" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="9" t="s">
         <v>27</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>695.22</v>
       </c>
     </row>
-    <row r="71" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="71" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
         <v>28</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>710.3</v>
       </c>
     </row>
-    <row r="72" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="72" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9" t="s">
         <v>29</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>671.03</v>
       </c>
     </row>
-    <row r="73" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="73" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
         <v>30</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>722.04</v>
       </c>
     </row>
-    <row r="74" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="74" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
         <v>31</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>721.93</v>
       </c>
     </row>
-    <row r="75" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="75" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="9" t="s">
         <v>32</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="76" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="76" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="9" t="s">
         <v>38</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>596.29999999999995</v>
       </c>
     </row>
-    <row r="77" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="77" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="9" t="s">
         <v>39</v>
       </c>
@@ -3433,7 +3433,7 @@
         <v>626.44000000000005</v>
       </c>
     </row>
-    <row r="78" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="78" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9" t="s">
         <v>34</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>637.66999999999996</v>
       </c>
     </row>
-    <row r="79" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="79" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="9" t="s">
         <v>40</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>708.09</v>
       </c>
     </row>
-    <row r="80" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="80" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="9" t="s">
         <v>11</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>847.19</v>
       </c>
     </row>
-    <row r="81" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="81" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="9" t="s">
         <v>12</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>790.45</v>
       </c>
     </row>
-    <row r="82" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="82" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="9" t="s">
         <v>13</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>774.73</v>
       </c>
     </row>
-    <row r="83" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="83" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9" t="s">
         <v>14</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>876.06</v>
       </c>
     </row>
-    <row r="84" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="84" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="9" t="s">
         <v>15</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>827.07</v>
       </c>
     </row>
-    <row r="85" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="85" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="9" t="s">
         <v>16</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>853.54</v>
       </c>
     </row>
-    <row r="86" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="86" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="9" t="s">
         <v>17</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>763.19</v>
       </c>
     </row>
-    <row r="87" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="87" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9" t="s">
         <v>18</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>802.8</v>
       </c>
     </row>
-    <row r="88" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="88" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="9" t="s">
         <v>19</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>797.01</v>
       </c>
     </row>
-    <row r="89" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="89" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="9" t="s">
         <v>20</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>819.8</v>
       </c>
     </row>
-    <row r="90" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="90" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="9" t="s">
         <v>21</v>
       </c>
@@ -3901,7 +3901,7 @@
         <v>829.57</v>
       </c>
     </row>
-    <row r="91" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="91" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9" t="s">
         <v>22</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>816.61</v>
       </c>
     </row>
-    <row r="92" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="92" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="9" t="s">
         <v>23</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>799.18</v>
       </c>
     </row>
-    <row r="93" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="93" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="9" t="s">
         <v>24</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>812.91</v>
       </c>
     </row>
-    <row r="94" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="94" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="9" t="s">
         <v>25</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>750.8</v>
       </c>
     </row>
-    <row r="95" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="95" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="9" t="s">
         <v>26</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>779.46</v>
       </c>
     </row>
-    <row r="96" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="96" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="9" t="s">
         <v>27</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>810.93</v>
       </c>
     </row>
-    <row r="97" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="97" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="9" t="s">
         <v>28</v>
       </c>
@@ -4153,7 +4153,7 @@
         <v>821.8</v>
       </c>
     </row>
-    <row r="98" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="98" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="9" t="s">
         <v>29</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>779.39</v>
       </c>
     </row>
-    <row r="99" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="99" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="9" t="s">
         <v>30</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>845.37</v>
       </c>
     </row>
-    <row r="100" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="100" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="9" t="s">
         <v>31</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>842.81</v>
       </c>
     </row>
-    <row r="101" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="101" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="9" t="s">
         <v>32</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>777.68</v>
       </c>
     </row>
-    <row r="102" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="102" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="9" t="s">
         <v>33</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>797.54</v>
       </c>
     </row>
-    <row r="103" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="103" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="9" t="s">
         <v>34</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>745.61</v>
       </c>
     </row>
-    <row r="104" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="104" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="9" t="s">
         <v>11</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>926.64</v>
       </c>
     </row>
-    <row r="105" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="105" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="9" t="s">
         <v>12</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>896.64</v>
       </c>
     </row>
-    <row r="106" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="106" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="9" t="s">
         <v>13</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>877.43</v>
       </c>
     </row>
-    <row r="107" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="107" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="9" t="s">
         <v>14</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>960.92</v>
       </c>
     </row>
-    <row r="108" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="108" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="9" t="s">
         <v>15</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>918.05</v>
       </c>
     </row>
-    <row r="109" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="109" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="9" t="s">
         <v>16</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>937.9</v>
       </c>
     </row>
-    <row r="110" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="110" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="9" t="s">
         <v>17</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>849.79</v>
       </c>
     </row>
-    <row r="111" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="111" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="9" t="s">
         <v>18</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>909.6</v>
       </c>
     </row>
-    <row r="112" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="112" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="9" t="s">
         <v>19</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>889.2</v>
       </c>
     </row>
-    <row r="113" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="113" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="9" t="s">
         <v>20</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>904.6</v>
       </c>
     </row>
-    <row r="114" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="114" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="9" t="s">
         <v>21</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>911.33</v>
       </c>
     </row>
-    <row r="115" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="115" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="9" t="s">
         <v>22</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>908.11</v>
       </c>
     </row>
-    <row r="116" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="116" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="9" t="s">
         <v>23</v>
       </c>
@@ -4837,7 +4837,7 @@
         <v>906.39</v>
       </c>
     </row>
-    <row r="117" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="117" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="9" t="s">
         <v>24</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>916.28</v>
       </c>
     </row>
-    <row r="118" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="118" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="9" t="s">
         <v>25</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>804.77</v>
       </c>
     </row>
-    <row r="119" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="119" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="9" t="s">
         <v>26</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>876.92</v>
       </c>
     </row>
-    <row r="120" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="120" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="9" t="s">
         <v>27</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>925.77</v>
       </c>
     </row>
-    <row r="121" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="121" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="9" t="s">
         <v>28</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>912.03</v>
       </c>
     </row>
-    <row r="122" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="122" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="9" t="s">
         <v>29</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>884.72</v>
       </c>
     </row>
-    <row r="123" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="123" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="9" t="s">
         <v>30</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>928.49</v>
       </c>
     </row>
-    <row r="124" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="124" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="9" t="s">
         <v>31</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>932.32</v>
       </c>
     </row>
-    <row r="125" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="125" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="9" t="s">
         <v>32</v>
       </c>
@@ -5161,7 +5161,7 @@
         <v>857.82</v>
       </c>
     </row>
-    <row r="126" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="126" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="9" t="s">
         <v>33</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>901.7</v>
       </c>
     </row>
-    <row r="127" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="127" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="9" t="s">
         <v>34</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>865.68</v>
       </c>
     </row>
-    <row r="128" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="128" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="9" t="s">
         <v>11</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>958.83</v>
       </c>
     </row>
-    <row r="129" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="129" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="9" t="s">
         <v>12</v>
       </c>
@@ -5305,7 +5305,7 @@
         <v>950.59</v>
       </c>
     </row>
-    <row r="130" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="130" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="9" t="s">
         <v>13</v>
       </c>
@@ -5341,7 +5341,7 @@
         <v>936.16</v>
       </c>
     </row>
-    <row r="131" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="131" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="9" t="s">
         <v>14</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>966.68</v>
       </c>
     </row>
-    <row r="132" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="132" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="9" t="s">
         <v>15</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>942.8</v>
       </c>
     </row>
-    <row r="133" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="133" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="9" t="s">
         <v>16</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>958.82</v>
       </c>
     </row>
-    <row r="134" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="134" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="9" t="s">
         <v>17</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>925.51</v>
       </c>
     </row>
-    <row r="135" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="135" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="9" t="s">
         <v>18</v>
       </c>
@@ -5521,7 +5521,7 @@
         <v>958.66</v>
       </c>
     </row>
-    <row r="136" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="136" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="9" t="s">
         <v>19</v>
       </c>
@@ -5557,7 +5557,7 @@
         <v>931.1</v>
       </c>
     </row>
-    <row r="137" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="137" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="9" t="s">
         <v>20</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>942.59</v>
       </c>
     </row>
-    <row r="138" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="138" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="9" t="s">
         <v>21</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>934.05</v>
       </c>
     </row>
-    <row r="139" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="139" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="9" t="s">
         <v>22</v>
       </c>
@@ -5665,7 +5665,7 @@
         <v>940.14</v>
       </c>
     </row>
-    <row r="140" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="140" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="9" t="s">
         <v>23</v>
       </c>
@@ -5701,7 +5701,7 @@
         <v>943.38</v>
       </c>
     </row>
-    <row r="141" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="141" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="9" t="s">
         <v>24</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>944.57</v>
       </c>
     </row>
-    <row r="142" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="142" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="9" t="s">
         <v>25</v>
       </c>
@@ -5773,7 +5773,7 @@
         <v>846.12</v>
       </c>
     </row>
-    <row r="143" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="143" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="9" t="s">
         <v>26</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>932.52</v>
       </c>
     </row>
-    <row r="144" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="144" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="9" t="s">
         <v>27</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>964.27</v>
       </c>
     </row>
-    <row r="145" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="145" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="9" t="s">
         <v>28</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>940.76</v>
       </c>
     </row>
-    <row r="146" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="146" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="9" t="s">
         <v>29</v>
       </c>
@@ -5917,7 +5917,7 @@
         <v>944.32</v>
       </c>
     </row>
-    <row r="147" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="147" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="9" t="s">
         <v>30</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>941.27</v>
       </c>
     </row>
-    <row r="148" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="148" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="9" t="s">
         <v>31</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>941.52</v>
       </c>
     </row>
-    <row r="149" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="149" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="9" t="s">
         <v>32</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>902.91</v>
       </c>
     </row>
-    <row r="150" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="150" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="9" t="s">
         <v>33</v>
       </c>
@@ -6061,7 +6061,7 @@
         <v>940.11</v>
       </c>
     </row>
-    <row r="151" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1">
+    <row r="151" spans="1:12" s="12" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="9" t="s">
         <v>34</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>917.25</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="21.75" thickBot="1">
+    <row r="152" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>11</v>
       </c>
@@ -6133,7 +6133,7 @@
         <v>483.63001902191979</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="21.75" thickBot="1">
+    <row r="153" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>12</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>471.9796990831025</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="21.75" thickBot="1">
+    <row r="154" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>13</v>
       </c>
@@ -6205,7 +6205,7 @@
         <v>493.76845693808036</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="21.75" thickBot="1">
+    <row r="155" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>14</v>
       </c>
@@ -6241,7 +6241,7 @@
         <v>505.17702686522352</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="21.75" thickBot="1">
+    <row r="156" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>15</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>488.05229391161532</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="21.75" thickBot="1">
+    <row r="157" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>16</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>520.8745525512129</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="21.75" thickBot="1">
+    <row r="158" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>17</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>482.6260545655756</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="21.75" thickBot="1">
+    <row r="159" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>18</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>483.44866897598428</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="21.75" thickBot="1">
+    <row r="160" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>19</v>
       </c>
@@ -6421,7 +6421,7 @@
         <v>463.37401636560901</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="21.75" thickBot="1">
+    <row r="161" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>20</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>527.36573327814097</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="21.75" thickBot="1">
+    <row r="162" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>21</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>515.63571631679781</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="21.75" thickBot="1">
+    <row r="163" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>22</v>
       </c>
@@ -6529,7 +6529,7 @@
         <v>490.99777323219564</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="21.75" thickBot="1">
+    <row r="164" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>23</v>
       </c>
@@ -6565,7 +6565,7 @@
         <v>446.88900930385239</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="21.75" thickBot="1">
+    <row r="165" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>24</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>516.32306575075438</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="21.75" thickBot="1">
+    <row r="166" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>25</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>412.33102076373655</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="21.75" thickBot="1">
+    <row r="167" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>26</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>530.54058798167034</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="21.75" thickBot="1">
+    <row r="168" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>27</v>
       </c>
@@ -6709,7 +6709,7 @@
         <v>439.08852618084654</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="21.75" thickBot="1">
+    <row r="169" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>28</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>500.48997040580167</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="21.75" thickBot="1">
+    <row r="170" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>29</v>
       </c>
@@ -6781,7 +6781,7 @@
         <v>512.46176309442455</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="21.75" thickBot="1">
+    <row r="171" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>30</v>
       </c>
@@ -6817,7 +6817,7 @@
         <v>464.00633033002453</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="21.75" thickBot="1">
+    <row r="172" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>31</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>516.3115256865301</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="21.75" thickBot="1">
+    <row r="173" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>32</v>
       </c>
@@ -6889,7 +6889,7 @@
         <v>470.62928714951721</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="21.75" thickBot="1">
+    <row r="174" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>33</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>499.16205129454488</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="21.75" thickBot="1">
+    <row r="175" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>34</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>504.83348314853424</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="21.75" thickBot="1">
+    <row r="176" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>11</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>623.93126800884113</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="21.75" thickBot="1">
+    <row r="177" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>12</v>
       </c>
@@ -7033,7 +7033,7 @@
         <v>585.88936431567515</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="21.75" thickBot="1">
+    <row r="178" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>13</v>
       </c>
@@ -7069,7 +7069,7 @@
         <v>599.14650713811</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="21.75" thickBot="1">
+    <row r="179" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>14</v>
       </c>
@@ -7105,7 +7105,7 @@
         <v>620.5441128156906</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="21.75" thickBot="1">
+    <row r="180" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>15</v>
       </c>
@@ -7141,7 +7141,7 @@
         <v>657.14176878262867</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="21.75" thickBot="1">
+    <row r="181" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>16</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>640.61662648535594</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="21.75" thickBot="1">
+    <row r="182" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>17</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>575.59373626367528</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="21.75" thickBot="1">
+    <row r="183" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>18</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>583.01963694765857</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="21.75" thickBot="1">
+    <row r="184" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>19</v>
       </c>
@@ -7285,7 +7285,7 @@
         <v>578.03440122043253</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="21.75" thickBot="1">
+    <row r="185" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>20</v>
       </c>
@@ -7321,7 +7321,7 @@
         <v>640.96150707127674</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="21.75" thickBot="1">
+    <row r="186" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>21</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>649.58255784712651</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="21.75" thickBot="1">
+    <row r="187" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>22</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>589.5156879808651</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="21.75" thickBot="1">
+    <row r="188" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>23</v>
       </c>
@@ -7429,7 +7429,7 @@
         <v>565.81176631722713</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="21.75" thickBot="1">
+    <row r="189" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>24</v>
       </c>
@@ -7465,7 +7465,7 @@
         <v>634.44350804786359</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="21.75" thickBot="1">
+    <row r="190" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>25</v>
       </c>
@@ -7501,7 +7501,7 @@
         <v>532.10117969280975</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="21.75" thickBot="1">
+    <row r="191" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>26</v>
       </c>
@@ -7537,7 +7537,7 @@
         <v>627.31478847249161</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="21.75" thickBot="1">
+    <row r="192" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>27</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>570.05862720524146</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="21.75" thickBot="1">
+    <row r="193" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>28</v>
       </c>
@@ -7609,7 +7609,7 @@
         <v>607.32960172126786</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="21.75" thickBot="1">
+    <row r="194" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>29</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>620.26497673244535</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="21.75" thickBot="1">
+    <row r="195" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>30</v>
       </c>
@@ -7681,7 +7681,7 @@
         <v>576.89532108296521</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="21.75" thickBot="1">
+    <row r="196" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>31</v>
       </c>
@@ -7717,7 +7717,7 @@
         <v>626.57278038321726</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="21.75" thickBot="1">
+    <row r="197" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>32</v>
       </c>
@@ -7753,7 +7753,7 @@
         <v>615.97121499767388</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="21.75" thickBot="1">
+    <row r="198" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>33</v>
       </c>
@@ -7789,7 +7789,7 @@
         <v>602.10386083698143</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="21.75" thickBot="1">
+    <row r="199" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>34</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>617.14079294282305</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="21.75" thickBot="1">
+    <row r="200" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>11</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>739.17463411421409</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="21.75" thickBot="1">
+    <row r="201" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>12</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>726.63754183191884</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="21.75" thickBot="1">
+    <row r="202" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>13</v>
       </c>
@@ -7933,7 +7933,7 @@
         <v>707.59592728440305</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="21.75" thickBot="1">
+    <row r="203" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>14</v>
       </c>
@@ -7969,7 +7969,7 @@
         <v>726.25076670268152</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="21.75" thickBot="1">
+    <row r="204" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>15</v>
       </c>
@@ -8005,7 +8005,7 @@
         <v>756.01515863168026</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="21.75" thickBot="1">
+    <row r="205" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>16</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>772.13008928168585</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="21.75" thickBot="1">
+    <row r="206" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>17</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>670.62439587616518</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="21.75" thickBot="1">
+    <row r="207" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>18</v>
       </c>
@@ -8113,7 +8113,7 @@
         <v>680.7589784175716</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="21.75" thickBot="1">
+    <row r="208" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>19</v>
       </c>
@@ -8149,7 +8149,7 @@
         <v>691.02234479484343</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="21.75" thickBot="1">
+    <row r="209" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>20</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>749.76099639489394</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="21.75" thickBot="1">
+    <row r="210" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>21</v>
       </c>
@@ -8221,7 +8221,7 @@
         <v>773.87566054714489</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="21.75" thickBot="1">
+    <row r="211" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>22</v>
       </c>
@@ -8257,7 +8257,7 @@
         <v>698.52656448933885</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="21.75" thickBot="1">
+    <row r="212" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>23</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>694.68294760559388</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="21.75" thickBot="1">
+    <row r="213" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>24</v>
       </c>
@@ -8329,7 +8329,7 @@
         <v>736.80934106449718</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="21.75" thickBot="1">
+    <row r="214" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>25</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>659.3267753002466</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="21.75" thickBot="1">
+    <row r="215" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>26</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>724.85311946859417</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="21.75" thickBot="1">
+    <row r="216" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>27</v>
       </c>
@@ -8437,7 +8437,7 @@
         <v>686.46136514010027</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="21.75" thickBot="1">
+    <row r="217" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>28</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>722.5310433310741</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="21.75" thickBot="1">
+    <row r="218" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>29</v>
       </c>
@@ -8509,7 +8509,7 @@
         <v>718.07660014532701</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="21.75" thickBot="1">
+    <row r="219" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>30</v>
       </c>
@@ -8545,7 +8545,7 @@
         <v>713.19496400983553</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="21.75" thickBot="1">
+    <row r="220" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>31</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>756.60830674684553</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="21.75" thickBot="1">
+    <row r="221" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>32</v>
       </c>
@@ -8617,7 +8617,7 @@
         <v>728.14885040968989</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="21.75" thickBot="1">
+    <row r="222" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>33</v>
       </c>
@@ -8653,7 +8653,7 @@
         <v>704.67554761818042</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="21.75" thickBot="1">
+    <row r="223" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>34</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>727.48627103847207</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="21.75" thickBot="1">
+    <row r="224" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>11</v>
       </c>
@@ -8725,7 +8725,7 @@
         <v>838.93767803920025</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="21.75" thickBot="1">
+    <row r="225" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>12</v>
       </c>
@@ -8761,7 +8761,7 @@
         <v>816.87605298733422</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="21.75" thickBot="1">
+    <row r="226" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>13</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>787.10902937873368</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="21.75" thickBot="1">
+    <row r="227" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>14</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>829.21581353796182</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="21.75" thickBot="1">
+    <row r="228" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>15</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>835.69496551736972</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="21.75" thickBot="1">
+    <row r="229" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>16</v>
       </c>
@@ -8905,7 +8905,7 @@
         <v>872.98008298190302</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="21.75" thickBot="1">
+    <row r="230" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>17</v>
       </c>
@@ -8941,7 +8941,7 @@
         <v>748.63789713579547</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="21.75" thickBot="1">
+    <row r="231" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>18</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>770.25065608750231</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="21.75" thickBot="1">
+    <row r="232" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>19</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>776.51072357128066</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="21.75" thickBot="1">
+    <row r="233" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>20</v>
       </c>
@@ -9049,7 +9049,7 @@
         <v>831.59239781856832</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="21.75" thickBot="1">
+    <row r="234" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>21</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>862.07114425813052</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="21.75" thickBot="1">
+    <row r="235" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>22</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>787.95076007947523</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="21.75" thickBot="1">
+    <row r="236" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>23</v>
       </c>
@@ -9157,7 +9157,7 @@
         <v>780.37433796458242</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="21.75" thickBot="1">
+    <row r="237" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>24</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>817.11187746523888</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="21.75" thickBot="1">
+    <row r="238" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>25</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>735.84118054471321</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="21.75" thickBot="1">
+    <row r="239" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>26</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>799.04387764495959</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="21.75" thickBot="1">
+    <row r="240" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>27</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>777.20510403562253</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="21.75" thickBot="1">
+    <row r="241" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>28</v>
       </c>
@@ -9337,7 +9337,7 @@
         <v>822.12875098965128</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="21.75" thickBot="1">
+    <row r="242" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>29</v>
       </c>
@@ -9373,7 +9373,7 @@
         <v>802.36942483715211</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="21.75" thickBot="1">
+    <row r="243" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>30</v>
       </c>
@@ -9409,7 +9409,7 @@
         <v>821.80852734610824</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="21.75" thickBot="1">
+    <row r="244" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>31</v>
       </c>
@@ -9445,7 +9445,7 @@
         <v>841.10577803493777</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="21.75" thickBot="1">
+    <row r="245" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>32</v>
       </c>
@@ -9481,7 +9481,7 @@
         <v>780.84407184475742</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="21.75" thickBot="1">
+    <row r="246" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>33</v>
       </c>
@@ -9517,7 +9517,7 @@
         <v>817.05445513027166</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="21.75" thickBot="1">
+    <row r="247" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>34</v>
       </c>
@@ -9553,7 +9553,7 @@
         <v>799.32852242927163</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="21.75" thickBot="1">
+    <row r="248" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A248" s="5" t="s">
         <v>11</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>914.13029946191386</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="21.75" thickBot="1">
+    <row r="249" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>12</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>908.71987830441822</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="21.75" thickBot="1">
+    <row r="250" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>13</v>
       </c>
@@ -9661,7 +9661,7 @@
         <v>868.58215232277234</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="21.75" thickBot="1">
+    <row r="251" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>14</v>
       </c>
@@ -9697,7 +9697,7 @@
         <v>920.86762214718829</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="21.75" thickBot="1">
+    <row r="252" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>15</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>917.66644207350328</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="21.75" thickBot="1">
+    <row r="253" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>16</v>
       </c>
@@ -9769,7 +9769,7 @@
         <v>947.03927099760233</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="21.75" thickBot="1">
+    <row r="254" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>17</v>
       </c>
@@ -9805,7 +9805,7 @@
         <v>849.78552043637433</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="21.75" thickBot="1">
+    <row r="255" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>18</v>
       </c>
@@ -9841,7 +9841,7 @@
         <v>873.98693399465913</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="21.75" thickBot="1">
+    <row r="256" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>19</v>
       </c>
@@ -9877,7 +9877,7 @@
         <v>869.09819890424671</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="21.75" thickBot="1">
+    <row r="257" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>20</v>
       </c>
@@ -9913,7 +9913,7 @@
         <v>917.01199294206515</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="21.75" thickBot="1">
+    <row r="258" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>21</v>
       </c>
@@ -9949,7 +9949,7 @@
         <v>924.3444437695332</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="21.75" thickBot="1">
+    <row r="259" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>22</v>
       </c>
@@ -9985,7 +9985,7 @@
         <v>896.85108529719355</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="21.75" thickBot="1">
+    <row r="260" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>23</v>
       </c>
@@ -10021,7 +10021,7 @@
         <v>857.78200601250126</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="21.75" thickBot="1">
+    <row r="261" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>24</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>909.77796546576621</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="21.75" thickBot="1">
+    <row r="262" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>25</v>
       </c>
@@ -10093,7 +10093,7 @@
         <v>794.12467521115502</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="21.75" thickBot="1">
+    <row r="263" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>26</v>
       </c>
@@ -10129,7 +10129,7 @@
         <v>878.02296154766645</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="21.75" thickBot="1">
+    <row r="264" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>27</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>897.49535731029255</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="21.75" thickBot="1">
+    <row r="265" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>28</v>
       </c>
@@ -10201,7 +10201,7 @@
         <v>901.2663218986479</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="21.75" thickBot="1">
+    <row r="266" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>29</v>
       </c>
@@ -10237,7 +10237,7 @@
         <v>896.52844601606182</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="21.75" thickBot="1">
+    <row r="267" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>30</v>
       </c>
@@ -10273,7 +10273,7 @@
         <v>919.07536277142231</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="21.75" thickBot="1">
+    <row r="268" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>31</v>
       </c>
@@ -10309,7 +10309,7 @@
         <v>918.95680013855895</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="21.75" thickBot="1">
+    <row r="269" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>32</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>845.95633097618429</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="21.75" thickBot="1">
+    <row r="270" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>33</v>
       </c>
@@ -10381,7 +10381,7 @@
         <v>893.93640191039287</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="21.75" thickBot="1">
+    <row r="271" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>34</v>
       </c>
@@ -10417,7 +10417,7 @@
         <v>898.62656885178194</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="21.75" thickBot="1">
+    <row r="272" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>11</v>
       </c>
@@ -10453,7 +10453,7 @@
         <v>946.44365979685961</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="21.75" thickBot="1">
+    <row r="273" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>12</v>
       </c>
@@ -10489,7 +10489,7 @@
         <v>939.50663628572124</v>
       </c>
     </row>
-    <row r="274" spans="1:12" ht="21.75" thickBot="1">
+    <row r="274" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>13</v>
       </c>
@@ -10525,7 +10525,7 @@
         <v>919.98078120576577</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="21.75" thickBot="1">
+    <row r="275" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>14</v>
       </c>
@@ -10561,7 +10561,7 @@
         <v>944.10883007705331</v>
       </c>
     </row>
-    <row r="276" spans="1:12" ht="21.75" thickBot="1">
+    <row r="276" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>15</v>
       </c>
@@ -10597,7 +10597,7 @@
         <v>928.65468596886126</v>
       </c>
     </row>
-    <row r="277" spans="1:12" ht="21.75" thickBot="1">
+    <row r="277" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
         <v>16</v>
       </c>
@@ -10633,7 +10633,7 @@
         <v>961.03201426828412</v>
       </c>
     </row>
-    <row r="278" spans="1:12" ht="21.75" thickBot="1">
+    <row r="278" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>17</v>
       </c>
@@ -10669,7 +10669,7 @@
         <v>929.80445991295312</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="21.75" thickBot="1">
+    <row r="279" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>18</v>
       </c>
@@ -10705,7 +10705,7 @@
         <v>935.27800040028069</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="21.75" thickBot="1">
+    <row r="280" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>19</v>
       </c>
@@ -10741,7 +10741,7 @@
         <v>913.09446440964427</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="21.75" thickBot="1">
+    <row r="281" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>20</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>950.86890413045228</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="21.75" thickBot="1">
+    <row r="282" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>21</v>
       </c>
@@ -10813,7 +10813,7 @@
         <v>939.53871997339922</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="21.75" thickBot="1">
+    <row r="283" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>22</v>
       </c>
@@ -10849,7 +10849,7 @@
         <v>934.59101043727139</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="21.75" thickBot="1">
+    <row r="284" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>23</v>
       </c>
@@ -10885,7 +10885,7 @@
         <v>922.03358742934324</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="21.75" thickBot="1">
+    <row r="285" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>24</v>
       </c>
@@ -10921,7 +10921,7 @@
         <v>938.70606870179677</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="21.75" thickBot="1">
+    <row r="286" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>25</v>
       </c>
@@ -10957,7 +10957,7 @@
         <v>840.93526359503846</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="21.75" thickBot="1">
+    <row r="287" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>26</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>929.38411549289424</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="21.75" thickBot="1">
+    <row r="288" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>27</v>
       </c>
@@ -11029,7 +11029,7 @@
         <v>947.41600915552249</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="21.75" thickBot="1">
+    <row r="289" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>28</v>
       </c>
@@ -11065,7 +11065,7 @@
         <v>923.71560049516734</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="21.75" thickBot="1">
+    <row r="290" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>29</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>949.49774711134114</v>
       </c>
     </row>
-    <row r="291" spans="1:12" ht="21.75" thickBot="1">
+    <row r="291" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>30</v>
       </c>
@@ -11137,7 +11137,7 @@
         <v>935.84662100772891</v>
       </c>
     </row>
-    <row r="292" spans="1:12" ht="21.75" thickBot="1">
+    <row r="292" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>31</v>
       </c>
@@ -11173,7 +11173,7 @@
         <v>937.17887908506532</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="21.75" thickBot="1">
+    <row r="293" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>32</v>
       </c>
@@ -11209,7 +11209,7 @@
         <v>884.54305674059947</v>
       </c>
     </row>
-    <row r="294" spans="1:12" ht="21.75" thickBot="1">
+    <row r="294" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>33</v>
       </c>
@@ -11245,7 +11245,7 @@
         <v>939.60807084420389</v>
       </c>
     </row>
-    <row r="295" spans="1:12" ht="21.75" thickBot="1">
+    <row r="295" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>34</v>
       </c>
@@ -11281,7 +11281,7 @@
         <v>931.71341099078131</v>
       </c>
     </row>
-    <row r="296" spans="1:12" ht="21.75" thickBot="1">
+    <row r="296" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>11</v>
       </c>
@@ -11319,7 +11319,7 @@
         <v>463.80709747340745</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="21.75" thickBot="1">
+    <row r="297" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>12</v>
       </c>
@@ -11357,7 +11357,7 @@
         <v>509.779255735893</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="21.75" thickBot="1">
+    <row r="298" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>13</v>
       </c>
@@ -11395,7 +11395,7 @@
         <v>508.43764615948845</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="21.75" thickBot="1">
+    <row r="299" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>14</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>551.58837853897785</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="21.75" thickBot="1">
+    <row r="300" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>15</v>
       </c>
@@ -11471,7 +11471,7 @@
         <v>514.80953003884827</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="21.75" thickBot="1">
+    <row r="301" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>16</v>
       </c>
@@ -11509,7 +11509,7 @@
         <v>532.64897714174049</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="21.75" thickBot="1">
+    <row r="302" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>17</v>
       </c>
@@ -11547,7 +11547,7 @@
         <v>523.4641558791443</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="21.75" thickBot="1">
+    <row r="303" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>18</v>
       </c>
@@ -11585,7 +11585,7 @@
         <v>482.35872777761529</v>
       </c>
     </row>
-    <row r="304" spans="1:12" ht="21.75" thickBot="1">
+    <row r="304" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>19</v>
       </c>
@@ -11623,7 +11623,7 @@
         <v>439.37030476884786</v>
       </c>
     </row>
-    <row r="305" spans="1:12" ht="21.75" thickBot="1">
+    <row r="305" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>20</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>516.92437748568875</v>
       </c>
     </row>
-    <row r="306" spans="1:12" ht="21.75" thickBot="1">
+    <row r="306" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>21</v>
       </c>
@@ -11699,7 +11699,7 @@
         <v>509.64134279991544</v>
       </c>
     </row>
-    <row r="307" spans="1:12" ht="21.75" thickBot="1">
+    <row r="307" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
         <v>22</v>
       </c>
@@ -11737,7 +11737,7 @@
         <v>530.58480932894827</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="21.75" thickBot="1">
+    <row r="308" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
         <v>23</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>459.45930791816983</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="21.75" thickBot="1">
+    <row r="309" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A309" s="2" t="s">
         <v>24</v>
       </c>
@@ -11813,7 +11813,7 @@
         <v>533.21314653384434</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="21.75" thickBot="1">
+    <row r="310" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
         <v>25</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>513.67975035674112</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="21.75" thickBot="1">
+    <row r="311" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
         <v>26</v>
       </c>
@@ -11889,7 +11889,7 @@
         <v>483.252629632631</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="21.75" thickBot="1">
+    <row r="312" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A312" s="2" t="s">
         <v>27</v>
       </c>
@@ -11927,7 +11927,7 @@
         <v>477.33895611897816</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="21.75" thickBot="1">
+    <row r="313" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A313" s="2" t="s">
         <v>28</v>
       </c>
@@ -11965,7 +11965,7 @@
         <v>534.4577540769003</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="21.75" thickBot="1">
+    <row r="314" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A314" s="2" t="s">
         <v>29</v>
       </c>
@@ -12003,7 +12003,7 @@
         <v>497.7841767466939</v>
       </c>
     </row>
-    <row r="315" spans="1:12" ht="21.75" thickBot="1">
+    <row r="315" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
         <v>30</v>
       </c>
@@ -12041,7 +12041,7 @@
         <v>476.23547691598753</v>
       </c>
     </row>
-    <row r="316" spans="1:12" ht="21.75" thickBot="1">
+    <row r="316" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A316" s="2" t="s">
         <v>31</v>
       </c>
@@ -12079,7 +12079,7 @@
         <v>586.24680398898033</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="21.75" thickBot="1">
+    <row r="317" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A317" s="2" t="s">
         <v>32</v>
       </c>
@@ -12117,7 +12117,7 @@
         <v>501.21121229136116</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="21.75" thickBot="1">
+    <row r="318" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A318" s="2" t="s">
         <v>33</v>
       </c>
@@ -12155,7 +12155,7 @@
         <v>496.72199126218618</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="21.75" thickBot="1">
+    <row r="319" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
         <v>34</v>
       </c>
@@ -12193,7 +12193,7 @@
         <v>500.04382922399441</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="21.75" thickBot="1">
+    <row r="320" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A320" s="2" t="s">
         <v>11</v>
       </c>
@@ -12231,7 +12231,7 @@
         <v>566.74544935638801</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="21.75" thickBot="1">
+    <row r="321" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A321" s="2" t="s">
         <v>12</v>
       </c>
@@ -12269,7 +12269,7 @@
         <v>576.60617046693437</v>
       </c>
     </row>
-    <row r="322" spans="1:12" ht="21.75" thickBot="1">
+    <row r="322" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
         <v>13</v>
       </c>
@@ -12307,7 +12307,7 @@
         <v>573.43586321035559</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="21.75" thickBot="1">
+    <row r="323" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A323" s="2" t="s">
         <v>14</v>
       </c>
@@ -12345,7 +12345,7 @@
         <v>653.19727488930027</v>
       </c>
     </row>
-    <row r="324" spans="1:12" ht="21.75" thickBot="1">
+    <row r="324" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A324" s="2" t="s">
         <v>15</v>
       </c>
@@ -12383,7 +12383,7 @@
         <v>629.39497758521293</v>
       </c>
     </row>
-    <row r="325" spans="1:12" ht="21.75" thickBot="1">
+    <row r="325" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A325" s="2" t="s">
         <v>16</v>
       </c>
@@ -12421,7 +12421,7 @@
         <v>612.78758666353565</v>
       </c>
     </row>
-    <row r="326" spans="1:12" ht="21.75" thickBot="1">
+    <row r="326" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A326" s="2" t="s">
         <v>17</v>
       </c>
@@ -12459,7 +12459,7 @@
         <v>605.89072788810847</v>
       </c>
     </row>
-    <row r="327" spans="1:12" ht="21.75" thickBot="1">
+    <row r="327" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A327" s="2" t="s">
         <v>18</v>
       </c>
@@ -12497,7 +12497,7 @@
         <v>588.85241739178355</v>
       </c>
     </row>
-    <row r="328" spans="1:12" ht="21.75" thickBot="1">
+    <row r="328" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A328" s="2" t="s">
         <v>19</v>
       </c>
@@ -12535,7 +12535,7 @@
         <v>522.75458740295301</v>
       </c>
     </row>
-    <row r="329" spans="1:12" ht="21.75" thickBot="1">
+    <row r="329" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A329" s="2" t="s">
         <v>20</v>
       </c>
@@ -12573,7 +12573,7 @@
         <v>613.15124287061303</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="21.75" thickBot="1">
+    <row r="330" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A330" s="2" t="s">
         <v>21</v>
       </c>
@@ -12611,7 +12611,7 @@
         <v>587.02109927820663</v>
       </c>
     </row>
-    <row r="331" spans="1:12" ht="21.75" thickBot="1">
+    <row r="331" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A331" s="2" t="s">
         <v>22</v>
       </c>
@@ -12649,7 +12649,7 @@
         <v>599.93244339994055</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="21.75" thickBot="1">
+    <row r="332" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2" t="s">
         <v>23</v>
       </c>
@@ -12687,7 +12687,7 @@
         <v>558.68589572993187</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="21.75" thickBot="1">
+    <row r="333" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
         <v>24</v>
       </c>
@@ -12725,7 +12725,7 @@
         <v>627.06667651693806</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="21.75" thickBot="1">
+    <row r="334" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A334" s="2" t="s">
         <v>25</v>
       </c>
@@ -12763,7 +12763,7 @@
         <v>611.45429374942137</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="21.75" thickBot="1">
+    <row r="335" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A335" s="2" t="s">
         <v>26</v>
       </c>
@@ -12801,7 +12801,7 @@
         <v>563.18976182615665</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="21.75" thickBot="1">
+    <row r="336" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A336" s="2" t="s">
         <v>27</v>
       </c>
@@ -12839,7 +12839,7 @@
         <v>575.30436674005148</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="21.75" thickBot="1">
+    <row r="337" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A337" s="2" t="s">
         <v>28</v>
       </c>
@@ -12877,7 +12877,7 @@
         <v>616.11811371583701</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="21.75" thickBot="1">
+    <row r="338" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2" t="s">
         <v>29</v>
       </c>
@@ -12915,7 +12915,7 @@
         <v>596.93188506653473</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="21.75" thickBot="1">
+    <row r="339" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A339" s="2" t="s">
         <v>30</v>
       </c>
@@ -12953,7 +12953,7 @@
         <v>590.18565468407382</v>
       </c>
     </row>
-    <row r="340" spans="1:12" ht="21.75" thickBot="1">
+    <row r="340" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
         <v>31</v>
       </c>
@@ -12991,7 +12991,7 @@
         <v>706.34407615246175</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="21.75" thickBot="1">
+    <row r="341" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A341" s="2" t="s">
         <v>32</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>592.99859016404776</v>
       </c>
     </row>
-    <row r="342" spans="1:12" ht="21.75" thickBot="1">
+    <row r="342" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
         <v>33</v>
       </c>
@@ -13067,7 +13067,7 @@
         <v>606.76279053188887</v>
       </c>
     </row>
-    <row r="343" spans="1:12" ht="21.75" thickBot="1">
+    <row r="343" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A343" s="2" t="s">
         <v>34</v>
       </c>
@@ -13105,7 +13105,7 @@
         <v>574.18175871755841</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="21.75" thickBot="1">
+    <row r="344" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A344" s="2" t="s">
         <v>11</v>
       </c>
@@ -13143,7 +13143,7 @@
         <v>692.72892451237726</v>
       </c>
     </row>
-    <row r="345" spans="1:12" ht="21.75" thickBot="1">
+    <row r="345" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A345" s="2" t="s">
         <v>12</v>
       </c>
@@ -13181,7 +13181,7 @@
         <v>690.05223140263877</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="21.75" thickBot="1">
+    <row r="346" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
         <v>13</v>
       </c>
@@ -13219,7 +13219,7 @@
         <v>659.84995327930926</v>
       </c>
     </row>
-    <row r="347" spans="1:12" ht="21.75" thickBot="1">
+    <row r="347" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A347" s="2" t="s">
         <v>14</v>
       </c>
@@ -13257,7 +13257,7 @@
         <v>778.97429287470641</v>
       </c>
     </row>
-    <row r="348" spans="1:12" ht="21.75" thickBot="1">
+    <row r="348" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A348" s="2" t="s">
         <v>15</v>
       </c>
@@ -13295,7 +13295,7 @@
         <v>744.66229222350046</v>
       </c>
     </row>
-    <row r="349" spans="1:12" ht="21.75" thickBot="1">
+    <row r="349" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A349" s="2" t="s">
         <v>16</v>
       </c>
@@ -13333,7 +13333,7 @@
         <v>734.01379882501976</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="21.75" thickBot="1">
+    <row r="350" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
         <v>17</v>
       </c>
@@ -13371,7 +13371,7 @@
         <v>700.44944026215171</v>
       </c>
     </row>
-    <row r="351" spans="1:12" ht="21.75" thickBot="1">
+    <row r="351" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A351" s="2" t="s">
         <v>18</v>
       </c>
@@ -13409,7 +13409,7 @@
         <v>694.57203953177577</v>
       </c>
     </row>
-    <row r="352" spans="1:12" ht="21.75" thickBot="1">
+    <row r="352" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
         <v>19</v>
       </c>
@@ -13447,7 +13447,7 @@
         <v>623.30303403509345</v>
       </c>
     </row>
-    <row r="353" spans="1:12" ht="21.75" thickBot="1">
+    <row r="353" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A353" s="2" t="s">
         <v>20</v>
       </c>
@@ -13485,7 +13485,7 @@
         <v>742.67642450943288</v>
       </c>
     </row>
-    <row r="354" spans="1:12" ht="21.75" thickBot="1">
+    <row r="354" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A354" s="2" t="s">
         <v>21</v>
       </c>
@@ -13523,7 +13523,7 @@
         <v>713.71624957011727</v>
       </c>
     </row>
-    <row r="355" spans="1:12" ht="21.75" thickBot="1">
+    <row r="355" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A355" s="2" t="s">
         <v>22</v>
       </c>
@@ -13561,7 +13561,7 @@
         <v>700.2349286611153</v>
       </c>
     </row>
-    <row r="356" spans="1:12" ht="21.75" thickBot="1">
+    <row r="356" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A356" s="2" t="s">
         <v>23</v>
       </c>
@@ -13599,7 +13599,7 @@
         <v>671.70933884125225</v>
       </c>
     </row>
-    <row r="357" spans="1:12" ht="21.75" thickBot="1">
+    <row r="357" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A357" s="2" t="s">
         <v>24</v>
       </c>
@@ -13637,7 +13637,7 @@
         <v>726.0276277056455</v>
       </c>
     </row>
-    <row r="358" spans="1:12" ht="21.75" thickBot="1">
+    <row r="358" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A358" s="2" t="s">
         <v>25</v>
       </c>
@@ -13675,7 +13675,7 @@
         <v>715.36458078680471</v>
       </c>
     </row>
-    <row r="359" spans="1:12" ht="21.75" thickBot="1">
+    <row r="359" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A359" s="2" t="s">
         <v>26</v>
       </c>
@@ -13713,7 +13713,7 @@
         <v>662.42887396647632</v>
       </c>
     </row>
-    <row r="360" spans="1:12" ht="21.75" thickBot="1">
+    <row r="360" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A360" s="2" t="s">
         <v>27</v>
       </c>
@@ -13751,7 +13751,7 @@
         <v>675.75275278778395</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="21.75" thickBot="1">
+    <row r="361" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A361" s="2" t="s">
         <v>28</v>
       </c>
@@ -13789,7 +13789,7 @@
         <v>727.51838703311068</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="21.75" thickBot="1">
+    <row r="362" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A362" s="2" t="s">
         <v>29</v>
       </c>
@@ -13827,7 +13827,7 @@
         <v>709.97962129494385</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="21.75" thickBot="1">
+    <row r="363" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A363" s="2" t="s">
         <v>30</v>
       </c>
@@ -13865,7 +13865,7 @@
         <v>729.8814090689084</v>
       </c>
     </row>
-    <row r="364" spans="1:12" ht="21.75" thickBot="1">
+    <row r="364" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A364" s="2" t="s">
         <v>31</v>
       </c>
@@ -13903,7 +13903,7 @@
         <v>809.38840633219843</v>
       </c>
     </row>
-    <row r="365" spans="1:12" ht="21.75" thickBot="1">
+    <row r="365" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A365" s="2" t="s">
         <v>32</v>
       </c>
@@ -13941,7 +13941,7 @@
         <v>690.19925219654783</v>
       </c>
     </row>
-    <row r="366" spans="1:12" ht="21.75" thickBot="1">
+    <row r="366" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A366" s="2" t="s">
         <v>33</v>
       </c>
@@ -13979,7 +13979,7 @@
         <v>737.64623648012264</v>
       </c>
     </row>
-    <row r="367" spans="1:12" ht="21.75" thickBot="1">
+    <row r="367" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A367" s="2" t="s">
         <v>34</v>
       </c>
@@ -14017,7 +14017,7 @@
         <v>689.85491217368076</v>
       </c>
     </row>
-    <row r="368" spans="1:12" ht="21.75" thickBot="1">
+    <row r="368" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A368" s="2" t="s">
         <v>11</v>
       </c>
@@ -14055,7 +14055,7 @@
         <v>830.98049475488097</v>
       </c>
     </row>
-    <row r="369" spans="1:12" ht="21.75" thickBot="1">
+    <row r="369" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A369" s="2" t="s">
         <v>12</v>
       </c>
@@ -14093,7 +14093,7 @@
         <v>804.01078592912233</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="21.75" thickBot="1">
+    <row r="370" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A370" s="2" t="s">
         <v>13</v>
       </c>
@@ -14131,7 +14131,7 @@
         <v>746.38754264203521</v>
       </c>
     </row>
-    <row r="371" spans="1:12" ht="21.75" thickBot="1">
+    <row r="371" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A371" s="2" t="s">
         <v>14</v>
       </c>
@@ -14169,7 +14169,7 @@
         <v>890.36654613724886</v>
       </c>
     </row>
-    <row r="372" spans="1:12" ht="21.75" thickBot="1">
+    <row r="372" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A372" s="2" t="s">
         <v>15</v>
       </c>
@@ -14207,7 +14207,7 @@
         <v>835.50624614524793</v>
       </c>
     </row>
-    <row r="373" spans="1:12" ht="21.75" thickBot="1">
+    <row r="373" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A373" s="2" t="s">
         <v>16</v>
       </c>
@@ -14245,7 +14245,7 @@
         <v>851.17941800758263</v>
       </c>
     </row>
-    <row r="374" spans="1:12" ht="21.75" thickBot="1">
+    <row r="374" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A374" s="2" t="s">
         <v>17</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>801.19597882857022</v>
       </c>
     </row>
-    <row r="375" spans="1:12" ht="21.75" thickBot="1">
+    <row r="375" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A375" s="2" t="s">
         <v>18</v>
       </c>
@@ -14321,7 +14321,7 @@
         <v>784.81531081690002</v>
       </c>
     </row>
-    <row r="376" spans="1:12" ht="21.75" thickBot="1">
+    <row r="376" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A376" s="2" t="s">
         <v>19</v>
       </c>
@@ -14359,7 +14359,7 @@
         <v>735.87698551271421</v>
       </c>
     </row>
-    <row r="377" spans="1:12" ht="21.75" thickBot="1">
+    <row r="377" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A377" s="2" t="s">
         <v>20</v>
       </c>
@@ -14397,7 +14397,7 @@
         <v>852.93336566207654</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="21.75" thickBot="1">
+    <row r="378" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A378" s="2" t="s">
         <v>21</v>
       </c>
@@ -14435,7 +14435,7 @@
         <v>832.94283613904952</v>
       </c>
     </row>
-    <row r="379" spans="1:12" ht="21.75" thickBot="1">
+    <row r="379" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A379" s="2" t="s">
         <v>22</v>
       </c>
@@ -14473,7 +14473,7 @@
         <v>798.60229387583445</v>
       </c>
     </row>
-    <row r="380" spans="1:12" ht="21.75" thickBot="1">
+    <row r="380" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A380" s="2" t="s">
         <v>23</v>
       </c>
@@ -14511,7 +14511,7 @@
         <v>776.92170121804179</v>
       </c>
     </row>
-    <row r="381" spans="1:12" ht="21.75" thickBot="1">
+    <row r="381" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A381" s="2" t="s">
         <v>24</v>
       </c>
@@ -14549,7 +14549,7 @@
         <v>831.87514703564386</v>
       </c>
     </row>
-    <row r="382" spans="1:12" ht="21.75" thickBot="1">
+    <row r="382" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A382" s="2" t="s">
         <v>25</v>
       </c>
@@ -14587,7 +14587,7 @@
         <v>812.47635595274937</v>
       </c>
     </row>
-    <row r="383" spans="1:12" ht="21.75" thickBot="1">
+    <row r="383" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A383" s="2" t="s">
         <v>26</v>
       </c>
@@ -14625,7 +14625,7 @@
         <v>755.80125209339258</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="21.75" thickBot="1">
+    <row r="384" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A384" s="2" t="s">
         <v>36</v>
       </c>
@@ -14663,7 +14663,7 @@
         <v>787.8713690530285</v>
       </c>
     </row>
-    <row r="385" spans="1:12" ht="21.75" thickBot="1">
+    <row r="385" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A385" s="2" t="s">
         <v>28</v>
       </c>
@@ -14701,7 +14701,7 @@
         <v>844.7169206627492</v>
       </c>
     </row>
-    <row r="386" spans="1:12" ht="21.75" thickBot="1">
+    <row r="386" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A386" s="2" t="s">
         <v>29</v>
       </c>
@@ -14739,7 +14739,7 @@
         <v>812.15205466711757</v>
       </c>
     </row>
-    <row r="387" spans="1:12" ht="21.75" thickBot="1">
+    <row r="387" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A387" s="2" t="s">
         <v>30</v>
       </c>
@@ -14777,7 +14777,7 @@
         <v>849.9219944806988</v>
       </c>
     </row>
-    <row r="388" spans="1:12" ht="21.75" thickBot="1">
+    <row r="388" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A388" s="2" t="s">
         <v>31</v>
       </c>
@@ -14815,7 +14815,7 @@
         <v>907.66922530923387</v>
       </c>
     </row>
-    <row r="389" spans="1:12" ht="21.75" thickBot="1">
+    <row r="389" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A389" s="2" t="s">
         <v>32</v>
       </c>
@@ -14853,7 +14853,7 @@
         <v>791.570771709729</v>
       </c>
     </row>
-    <row r="390" spans="1:12" ht="21.75" thickBot="1">
+    <row r="390" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A390" s="2" t="s">
         <v>33</v>
       </c>
@@ -14891,7 +14891,7 @@
         <v>877.52653380324682</v>
       </c>
     </row>
-    <row r="391" spans="1:12" ht="21.75" thickBot="1">
+    <row r="391" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A391" s="2" t="s">
         <v>11</v>
       </c>
@@ -14929,7 +14929,7 @@
         <v>900.06015018671644</v>
       </c>
     </row>
-    <row r="392" spans="1:12" ht="21.75" thickBot="1">
+    <row r="392" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A392" s="2" t="s">
         <v>12</v>
       </c>
@@ -14967,7 +14967,7 @@
         <v>899.53618639035551</v>
       </c>
     </row>
-    <row r="393" spans="1:12" ht="21.75" thickBot="1">
+    <row r="393" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A393" s="2" t="s">
         <v>13</v>
       </c>
@@ -15005,7 +15005,7 @@
         <v>865.41655566009058</v>
       </c>
     </row>
-    <row r="394" spans="1:12" ht="21.75" thickBot="1">
+    <row r="394" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A394" s="2" t="s">
         <v>14</v>
       </c>
@@ -15043,7 +15043,7 @@
         <v>947.98417858338166</v>
       </c>
     </row>
-    <row r="395" spans="1:12" ht="21.75" thickBot="1">
+    <row r="395" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A395" s="2" t="s">
         <v>15</v>
       </c>
@@ -15081,7 +15081,7 @@
         <v>907.88644919026763</v>
       </c>
     </row>
-    <row r="396" spans="1:12" ht="21.75" thickBot="1">
+    <row r="396" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A396" s="2" t="s">
         <v>16</v>
       </c>
@@ -15119,7 +15119,7 @@
         <v>935.39645717663825</v>
       </c>
     </row>
-    <row r="397" spans="1:12" ht="21.75" thickBot="1">
+    <row r="397" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A397" s="2" t="s">
         <v>17</v>
       </c>
@@ -15157,7 +15157,7 @@
         <v>875.67531750753335</v>
       </c>
     </row>
-    <row r="398" spans="1:12" ht="21.75" thickBot="1">
+    <row r="398" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A398" s="2" t="s">
         <v>18</v>
       </c>
@@ -15195,7 +15195,7 @@
         <v>889.26924861181578</v>
       </c>
     </row>
-    <row r="399" spans="1:12" ht="21.75" thickBot="1">
+    <row r="399" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A399" s="2" t="s">
         <v>19</v>
       </c>
@@ -15233,7 +15233,7 @@
         <v>839.8697780532558</v>
       </c>
     </row>
-    <row r="400" spans="1:12" ht="21.75" thickBot="1">
+    <row r="400" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A400" s="2" t="s">
         <v>20</v>
       </c>
@@ -15271,7 +15271,7 @@
         <v>928.66794245953622</v>
       </c>
     </row>
-    <row r="401" spans="1:12" ht="21.75" thickBot="1">
+    <row r="401" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A401" s="2" t="s">
         <v>21</v>
       </c>
@@ -15309,7 +15309,7 @@
         <v>907.37660970512889</v>
       </c>
     </row>
-    <row r="402" spans="1:12" ht="21.75" thickBot="1">
+    <row r="402" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A402" s="2" t="s">
         <v>22</v>
       </c>
@@ -15347,7 +15347,7 @@
         <v>884.43390015507305</v>
       </c>
     </row>
-    <row r="403" spans="1:12" ht="21.75" thickBot="1">
+    <row r="403" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A403" s="2" t="s">
         <v>23</v>
       </c>
@@ -15385,7 +15385,7 @@
         <v>882.26890772932245</v>
       </c>
     </row>
-    <row r="404" spans="1:12" ht="21.75" thickBot="1">
+    <row r="404" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A404" s="2" t="s">
         <v>24</v>
       </c>
@@ -15423,7 +15423,7 @@
         <v>925.31150379664871</v>
       </c>
     </row>
-    <row r="405" spans="1:12" ht="21.75" thickBot="1">
+    <row r="405" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A405" s="2" t="s">
         <v>25</v>
       </c>
@@ -15461,7 +15461,7 @@
         <v>892.93947176521829</v>
       </c>
     </row>
-    <row r="406" spans="1:12" ht="21.75" thickBot="1">
+    <row r="406" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A406" s="2" t="s">
         <v>26</v>
       </c>
@@ -15499,7 +15499,7 @@
         <v>871.41225615260407</v>
       </c>
     </row>
-    <row r="407" spans="1:12" ht="21.75" thickBot="1">
+    <row r="407" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A407" s="2" t="s">
         <v>36</v>
       </c>
@@ -15537,7 +15537,7 @@
         <v>907.48954188362973</v>
       </c>
     </row>
-    <row r="408" spans="1:12" ht="21.75" thickBot="1">
+    <row r="408" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A408" s="2" t="s">
         <v>28</v>
       </c>
@@ -15575,7 +15575,7 @@
         <v>930.12694551196398</v>
       </c>
     </row>
-    <row r="409" spans="1:12" ht="21.75" thickBot="1">
+    <row r="409" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A409" s="2" t="s">
         <v>29</v>
       </c>
@@ -15613,7 +15613,7 @@
         <v>912.51423359104774</v>
       </c>
     </row>
-    <row r="410" spans="1:12" ht="21.75" thickBot="1">
+    <row r="410" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A410" s="2" t="s">
         <v>30</v>
       </c>
@@ -15651,7 +15651,7 @@
         <v>922.81158638187833</v>
       </c>
     </row>
-    <row r="411" spans="1:12" ht="21.75" thickBot="1">
+    <row r="411" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A411" s="2" t="s">
         <v>31</v>
       </c>
@@ -15689,7 +15689,7 @@
         <v>946.89973932344765</v>
       </c>
     </row>
-    <row r="412" spans="1:12" ht="21.75" thickBot="1">
+    <row r="412" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A412" s="2" t="s">
         <v>32</v>
       </c>
@@ -15727,7 +15727,7 @@
         <v>892.16898882730118</v>
       </c>
     </row>
-    <row r="413" spans="1:12" ht="21.75" thickBot="1">
+    <row r="413" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A413" s="2" t="s">
         <v>33</v>
       </c>
@@ -15763,6 +15763,880 @@
       </c>
       <c r="L413">
         <v>951.63416939257718</v>
+      </c>
+    </row>
+    <row r="414" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A414" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B414" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C414" s="3">
+        <v>0.93241867096224706</v>
+      </c>
+      <c r="D414" s="3">
+        <v>0.98642266824085001</v>
+      </c>
+      <c r="E414" s="3">
+        <v>0.88961341406613881</v>
+      </c>
+      <c r="F414" s="3">
+        <v>1</v>
+      </c>
+      <c r="G414" s="3">
+        <v>1</v>
+      </c>
+      <c r="H414" s="2">
+        <v>94.932466281310226</v>
+      </c>
+      <c r="I414" s="2">
+        <v>0</v>
+      </c>
+      <c r="J414" s="2">
+        <v>0</v>
+      </c>
+      <c r="K414" s="2">
+        <v>0</v>
+      </c>
+      <c r="L414">
+        <v>951.4050021346311</v>
+      </c>
+    </row>
+    <row r="415" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A415" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B415" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C415" s="3">
+        <v>0.9375</v>
+      </c>
+      <c r="D415" s="3">
+        <v>0.97046632124352328</v>
+      </c>
+      <c r="E415" s="3">
+        <v>0.86189093816816453</v>
+      </c>
+      <c r="F415" s="3">
+        <v>0.98618058371143702</v>
+      </c>
+      <c r="G415" s="3">
+        <v>1</v>
+      </c>
+      <c r="H415" s="2">
+        <v>93.972544378698231</v>
+      </c>
+      <c r="I415" s="2">
+        <v>0</v>
+      </c>
+      <c r="J415" s="2">
+        <v>0</v>
+      </c>
+      <c r="K415" s="2">
+        <v>0</v>
+      </c>
+      <c r="L415">
+        <v>950.26223487419418</v>
+      </c>
+    </row>
+    <row r="416" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A416" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B416" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C416" s="3">
+        <v>0.92372206502770204</v>
+      </c>
+      <c r="D416" s="3">
+        <v>0.96489563567362424</v>
+      </c>
+      <c r="E416" s="3">
+        <v>0.83601286173633438</v>
+      </c>
+      <c r="F416" s="3">
+        <v>1.03</v>
+      </c>
+      <c r="G416" s="3">
+        <v>1</v>
+      </c>
+      <c r="H416" s="2">
+        <v>93.038413241508394</v>
+      </c>
+      <c r="I416" s="2">
+        <v>0</v>
+      </c>
+      <c r="J416" s="2">
+        <v>0</v>
+      </c>
+      <c r="K416" s="2">
+        <v>0</v>
+      </c>
+      <c r="L416">
+        <v>945.57511257410692</v>
+      </c>
+    </row>
+    <row r="417" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A417" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B417" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C417" s="3">
+        <v>0.94613330191272926</v>
+      </c>
+      <c r="D417" s="3">
+        <v>0.98608903020667726</v>
+      </c>
+      <c r="E417" s="3">
+        <v>0.92436714843011569</v>
+      </c>
+      <c r="F417" s="3">
+        <v>0.96574784154004856</v>
+      </c>
+      <c r="G417" s="3">
+        <v>1</v>
+      </c>
+      <c r="H417" s="2">
+        <v>92.524059259259261</v>
+      </c>
+      <c r="I417" s="2">
+        <v>0</v>
+      </c>
+      <c r="J417" s="2">
+        <v>0</v>
+      </c>
+      <c r="K417" s="2">
+        <v>0</v>
+      </c>
+      <c r="L417">
+        <v>958.08106248593299</v>
+      </c>
+    </row>
+    <row r="418" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A418" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B418" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C418" s="3">
+        <v>0.90658631990696692</v>
+      </c>
+      <c r="D418" s="3">
+        <v>0.98441396508728185</v>
+      </c>
+      <c r="E418" s="3">
+        <v>0.87967788790157209</v>
+      </c>
+      <c r="F418" s="3">
+        <v>0.95436317497740131</v>
+      </c>
+      <c r="G418" s="3">
+        <v>1</v>
+      </c>
+      <c r="H418" s="2">
+        <v>94.746511204481777</v>
+      </c>
+      <c r="I418" s="2">
+        <v>0</v>
+      </c>
+      <c r="J418" s="2">
+        <v>0</v>
+      </c>
+      <c r="K418" s="2">
+        <v>0</v>
+      </c>
+      <c r="L418">
+        <v>932.24670115978188</v>
+      </c>
+    </row>
+    <row r="419" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A419" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B419" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C419" s="3">
+        <v>0.95437704322557215</v>
+      </c>
+      <c r="D419" s="3">
+        <v>0.99819819819819822</v>
+      </c>
+      <c r="E419" s="3">
+        <v>0.88631041498713958</v>
+      </c>
+      <c r="F419" s="3">
+        <v>0.97077300353198026</v>
+      </c>
+      <c r="G419" s="3">
+        <v>1</v>
+      </c>
+      <c r="H419" s="2">
+        <v>93.671209846435261</v>
+      </c>
+      <c r="I419" s="2">
+        <v>0</v>
+      </c>
+      <c r="J419" s="2">
+        <v>0</v>
+      </c>
+      <c r="K419" s="2">
+        <v>0</v>
+      </c>
+      <c r="L419">
+        <v>960.47570379351782</v>
+      </c>
+    </row>
+    <row r="420" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A420" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B420" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C420" s="3">
+        <v>0.91801360221163142</v>
+      </c>
+      <c r="D420" s="3">
+        <v>0.99878296146044621</v>
+      </c>
+      <c r="E420" s="3">
+        <v>0.88012731108965414</v>
+      </c>
+      <c r="F420" s="3">
+        <v>1</v>
+      </c>
+      <c r="G420" s="3">
+        <v>1</v>
+      </c>
+      <c r="H420" s="2">
+        <v>93.092119975515203</v>
+      </c>
+      <c r="I420" s="2">
+        <v>0</v>
+      </c>
+      <c r="J420" s="2">
+        <v>0</v>
+      </c>
+      <c r="K420" s="2">
+        <v>0</v>
+      </c>
+      <c r="L420">
+        <v>942.87789733795705</v>
+      </c>
+    </row>
+    <row r="421" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A421" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B421" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C421" s="3">
+        <v>0.94028182786498804</v>
+      </c>
+      <c r="D421" s="3">
+        <v>0.97319978343259339</v>
+      </c>
+      <c r="E421" s="3">
+        <v>0.91321242162968252</v>
+      </c>
+      <c r="F421" s="3">
+        <v>0.93999874345971102</v>
+      </c>
+      <c r="G421" s="3">
+        <v>1</v>
+      </c>
+      <c r="H421" s="2">
+        <v>92.794901226408172</v>
+      </c>
+      <c r="I421" s="2">
+        <v>0</v>
+      </c>
+      <c r="J421" s="2">
+        <v>0</v>
+      </c>
+      <c r="K421" s="2">
+        <v>0</v>
+      </c>
+      <c r="L421">
+        <v>951.26975924138196</v>
+      </c>
+    </row>
+    <row r="422" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A422" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B422" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C422" s="3">
+        <v>0.88669412976313078</v>
+      </c>
+      <c r="D422" s="3">
+        <v>1</v>
+      </c>
+      <c r="E422" s="3">
+        <v>0.86906193922423147</v>
+      </c>
+      <c r="F422" s="3">
+        <v>0.8514736294837133</v>
+      </c>
+      <c r="G422" s="3">
+        <v>1</v>
+      </c>
+      <c r="H422" s="2">
+        <v>93.163522875816994</v>
+      </c>
+      <c r="I422" s="2">
+        <v>0</v>
+      </c>
+      <c r="J422" s="2">
+        <v>-5</v>
+      </c>
+      <c r="K422" s="2">
+        <v>0</v>
+      </c>
+      <c r="L422">
+        <v>905.99265719391019</v>
+      </c>
+    </row>
+    <row r="423" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A423" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B423" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C423" s="3">
+        <v>0.94740119561607439</v>
+      </c>
+      <c r="D423" s="3">
+        <v>0.9795627376425855</v>
+      </c>
+      <c r="E423" s="3">
+        <v>0.90432954777683705</v>
+      </c>
+      <c r="F423" s="3">
+        <v>1</v>
+      </c>
+      <c r="G423" s="3">
+        <v>1</v>
+      </c>
+      <c r="H423" s="2">
+        <v>94.616222440087157</v>
+      </c>
+      <c r="I423" s="2">
+        <v>0</v>
+      </c>
+      <c r="J423" s="2">
+        <v>0</v>
+      </c>
+      <c r="K423" s="2">
+        <v>0</v>
+      </c>
+      <c r="L423">
+        <v>963.64315379318668</v>
+      </c>
+    </row>
+    <row r="424" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A424" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B424" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C424" s="3">
+        <v>0.93436857123896744</v>
+      </c>
+      <c r="D424" s="3">
+        <v>0.94880694143167033</v>
+      </c>
+      <c r="E424" s="3">
+        <v>0.86949944994499451</v>
+      </c>
+      <c r="F424" s="3">
+        <v>0.91891380903637543</v>
+      </c>
+      <c r="G424" s="3">
+        <v>1</v>
+      </c>
+      <c r="H424" s="2">
+        <v>94.646052631578954</v>
+      </c>
+      <c r="I424" s="2">
+        <v>0</v>
+      </c>
+      <c r="J424" s="2">
+        <v>0</v>
+      </c>
+      <c r="K424" s="2">
+        <v>0</v>
+      </c>
+      <c r="L424">
+        <v>940.32084185981569</v>
+      </c>
+    </row>
+    <row r="425" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A425" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B425" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C425" s="3">
+        <v>0.91904074067628483</v>
+      </c>
+      <c r="D425" s="3">
+        <v>0.99845995893223816</v>
+      </c>
+      <c r="E425" s="3">
+        <v>0.8903389028429981</v>
+      </c>
+      <c r="F425" s="3">
+        <v>0.97946392872768206</v>
+      </c>
+      <c r="G425" s="3">
+        <v>1</v>
+      </c>
+      <c r="H425" s="2">
+        <v>91.701903559403561</v>
+      </c>
+      <c r="I425" s="2">
+        <v>0</v>
+      </c>
+      <c r="J425" s="2">
+        <v>0</v>
+      </c>
+      <c r="K425" s="2">
+        <v>0</v>
+      </c>
+      <c r="L425">
+        <v>939.96669969735228</v>
+      </c>
+    </row>
+    <row r="426" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A426" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B426" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C426" s="3">
+        <v>0.93299199681861111</v>
+      </c>
+      <c r="D426" s="3">
+        <v>0.95171537484116897</v>
+      </c>
+      <c r="E426" s="3">
+        <v>0.82471258283754312</v>
+      </c>
+      <c r="F426" s="3">
+        <v>0.93921172493825344</v>
+      </c>
+      <c r="G426" s="3">
+        <v>1</v>
+      </c>
+      <c r="H426" s="2">
+        <v>94.489563857195421</v>
+      </c>
+      <c r="I426" s="2">
+        <v>0</v>
+      </c>
+      <c r="J426" s="2">
+        <v>0</v>
+      </c>
+      <c r="K426" s="2">
+        <v>0</v>
+      </c>
+      <c r="L426">
+        <v>941.72787208537386</v>
+      </c>
+    </row>
+    <row r="427" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A427" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B427" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C427" s="3">
+        <v>0.92478570566219964</v>
+      </c>
+      <c r="D427" s="3">
+        <v>1</v>
+      </c>
+      <c r="E427" s="3">
+        <v>0.84662775033677595</v>
+      </c>
+      <c r="F427" s="3">
+        <v>0.98116934183582638</v>
+      </c>
+      <c r="G427" s="3">
+        <v>1</v>
+      </c>
+      <c r="H427" s="2">
+        <v>94.68822210901682</v>
+      </c>
+      <c r="I427" s="2">
+        <v>0</v>
+      </c>
+      <c r="J427" s="2">
+        <v>0</v>
+      </c>
+      <c r="K427" s="2">
+        <v>0</v>
+      </c>
+      <c r="L427">
+        <v>946.4372944068092</v>
+      </c>
+    </row>
+    <row r="428" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A428" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B428" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C428" s="3">
+        <v>0.90721640333747555</v>
+      </c>
+      <c r="D428" s="3">
+        <v>0.92810331534309942</v>
+      </c>
+      <c r="E428" s="3">
+        <v>0.88113035551504104</v>
+      </c>
+      <c r="F428" s="3">
+        <v>1.0189587191021969</v>
+      </c>
+      <c r="G428" s="3">
+        <v>1</v>
+      </c>
+      <c r="H428" s="2">
+        <v>92.912522366522381</v>
+      </c>
+      <c r="I428" s="2">
+        <v>0</v>
+      </c>
+      <c r="J428" s="2">
+        <v>0</v>
+      </c>
+      <c r="K428" s="2">
+        <v>0</v>
+      </c>
+      <c r="L428">
+        <v>931.58774764666362</v>
+      </c>
+    </row>
+    <row r="429" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A429" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B429" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C429" s="3">
+        <v>0.90123128709363098</v>
+      </c>
+      <c r="D429" s="3">
+        <v>1</v>
+      </c>
+      <c r="E429" s="3">
+        <v>0.8516852219002593</v>
+      </c>
+      <c r="F429" s="3">
+        <v>1.014382739378068</v>
+      </c>
+      <c r="G429" s="3">
+        <v>1</v>
+      </c>
+      <c r="H429" s="2">
+        <v>92.60895638045244</v>
+      </c>
+      <c r="I429" s="2">
+        <v>0</v>
+      </c>
+      <c r="J429" s="2">
+        <v>0</v>
+      </c>
+      <c r="K429" s="2">
+        <v>0</v>
+      </c>
+      <c r="L429">
+        <v>934.72443821975628</v>
+      </c>
+    </row>
+    <row r="430" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A430" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B430" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C430" s="3">
+        <v>0.94246950622920878</v>
+      </c>
+      <c r="D430" s="3">
+        <v>0.9515962924819773</v>
+      </c>
+      <c r="E430" s="3">
+        <v>0.90160997832721479</v>
+      </c>
+      <c r="F430" s="3">
+        <v>0.93030179746134001</v>
+      </c>
+      <c r="G430" s="3">
+        <v>1</v>
+      </c>
+      <c r="H430" s="2">
+        <v>93.194614853195176</v>
+      </c>
+      <c r="I430" s="2">
+        <v>0</v>
+      </c>
+      <c r="J430" s="2">
+        <v>0</v>
+      </c>
+      <c r="K430" s="2">
+        <v>0</v>
+      </c>
+      <c r="L430">
+        <v>949.7426522735916</v>
+      </c>
+    </row>
+    <row r="431" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A431" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B431" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C431" s="3">
+        <v>0.9336584172793837</v>
+      </c>
+      <c r="D431" s="3">
+        <v>1</v>
+      </c>
+      <c r="E431" s="3">
+        <v>0.92383383094160321</v>
+      </c>
+      <c r="F431" s="3">
+        <v>0.99282246778466698</v>
+      </c>
+      <c r="G431" s="3">
+        <v>1</v>
+      </c>
+      <c r="H431" s="2">
+        <v>95.215508241758243</v>
+      </c>
+      <c r="I431" s="2">
+        <v>0</v>
+      </c>
+      <c r="J431" s="2">
+        <v>0</v>
+      </c>
+      <c r="K431" s="2">
+        <v>0</v>
+      </c>
+      <c r="L431">
+        <v>958.00988452388606</v>
+      </c>
+    </row>
+    <row r="432" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A432" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B432" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C432" s="3">
+        <v>0.94400916005561464</v>
+      </c>
+      <c r="D432" s="3">
+        <v>0.96356275303643724</v>
+      </c>
+      <c r="E432" s="3">
+        <v>0.90486896528051897</v>
+      </c>
+      <c r="F432" s="3">
+        <v>1.03</v>
+      </c>
+      <c r="G432" s="3">
+        <v>1</v>
+      </c>
+      <c r="H432" s="2">
+        <v>93.930456121632417</v>
+      </c>
+      <c r="I432" s="2">
+        <v>0</v>
+      </c>
+      <c r="J432" s="2">
+        <v>0</v>
+      </c>
+      <c r="K432" s="2">
+        <v>0</v>
+      </c>
+      <c r="L432">
+        <v>962.4917694558643</v>
+      </c>
+    </row>
+    <row r="433" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A433" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B433" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C433" s="3">
+        <v>0.91520404761437846</v>
+      </c>
+      <c r="D433" s="3">
+        <v>0.88414889167712252</v>
+      </c>
+      <c r="E433" s="3">
+        <v>0.83078109048482196</v>
+      </c>
+      <c r="F433" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="G433" s="3">
+        <v>1</v>
+      </c>
+      <c r="H433" s="2">
+        <v>94.201406936241099</v>
+      </c>
+      <c r="I433" s="2">
+        <v>0</v>
+      </c>
+      <c r="J433" s="2">
+        <v>0</v>
+      </c>
+      <c r="K433" s="2">
+        <v>0</v>
+      </c>
+      <c r="L433">
+        <v>932.97852229186151</v>
+      </c>
+    </row>
+    <row r="434" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A434" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B434" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C434" s="3">
+        <v>0.93091554153937128</v>
+      </c>
+      <c r="D434" s="3">
+        <v>0.9982698961937716</v>
+      </c>
+      <c r="E434" s="3">
+        <v>0.91382724126650716</v>
+      </c>
+      <c r="F434" s="3">
+        <v>1</v>
+      </c>
+      <c r="G434" s="3">
+        <v>1</v>
+      </c>
+      <c r="H434" s="2">
+        <v>93.593328725038418</v>
+      </c>
+      <c r="I434" s="2">
+        <v>0</v>
+      </c>
+      <c r="J434" s="2">
+        <v>0</v>
+      </c>
+      <c r="K434" s="2">
+        <v>0</v>
+      </c>
+      <c r="L434">
+        <v>955.42386619106981</v>
+      </c>
+    </row>
+    <row r="435" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A435" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B435" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C435" s="3">
+        <v>0.90204728619991592</v>
+      </c>
+      <c r="D435" s="3">
+        <v>1</v>
+      </c>
+      <c r="E435" s="3">
+        <v>0.75229481902332507</v>
+      </c>
+      <c r="F435" s="3">
+        <v>1</v>
+      </c>
+      <c r="G435" s="3">
+        <v>1</v>
+      </c>
+      <c r="H435" s="2">
+        <v>93.42034965034965</v>
+      </c>
+      <c r="I435" s="2">
+        <v>0</v>
+      </c>
+      <c r="J435" s="2">
+        <v>0</v>
+      </c>
+      <c r="K435" s="2">
+        <v>0</v>
+      </c>
+      <c r="L435">
+        <v>929.54635706030331</v>
+      </c>
+    </row>
+    <row r="436" spans="1:12" ht="21.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A436" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B436" s="4">
+        <v>46174</v>
+      </c>
+      <c r="C436" s="3">
+        <v>0.94843185783259631</v>
+      </c>
+      <c r="D436" s="3">
+        <v>0.98669254227890213</v>
+      </c>
+      <c r="E436" s="3">
+        <v>0.92456968435096376</v>
+      </c>
+      <c r="F436" s="3">
+        <v>1.02</v>
+      </c>
+      <c r="G436" s="3">
+        <v>1</v>
+      </c>
+      <c r="H436" s="2">
+        <v>93.66317238769588</v>
+      </c>
+      <c r="I436" s="2">
+        <v>0</v>
+      </c>
+      <c r="J436" s="2">
+        <v>0</v>
+      </c>
+      <c r="K436" s="2">
+        <v>0</v>
+      </c>
+      <c r="L436">
+        <v>965.9699484235141</v>
       </c>
     </row>
   </sheetData>
